--- a/data/SPR_BS_master.xlsx
+++ b/data/SPR_BS_master.xlsx
@@ -11,7 +11,7 @@
     <sheet name="master_bono" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="README" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="true" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="119">
   <si>
     <t xml:space="preserve">codigo</t>
   </si>
@@ -50,19 +50,307 @@
     <t xml:space="preserve">valor_residual</t>
   </si>
   <si>
+    <t xml:space="preserve">PARP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parcial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DICP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAP0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL29D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AN29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bullet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AN29D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL30</t>
+  </si>
+  <si>
     <t xml:space="preserve">AL30D</t>
   </si>
   <si>
-    <t xml:space="preserve">USD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parcial</t>
+    <t xml:space="preserve">AL35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL35D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AE38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AE38D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL41D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GD29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GD29D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GD30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GD30D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GD35</t>
   </si>
   <si>
     <t xml:space="preserve">GD35D</t>
   </si>
   <si>
-    <t xml:space="preserve">AL41D</t>
+    <t xml:space="preserve">GD38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GD38D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GD41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GD41D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GD46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GD46D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TO26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TY30P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARS CER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TZX26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X31L6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TZX27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TZX28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TZXD6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TZXD7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TZXM6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TZXM7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TZXO6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TZV26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARS USD LINKED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D30A6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPOA7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPOB7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPOC7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPOD7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPA7C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USD CCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPB7C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPC7C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPD7C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPA7D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USD MEP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPB7D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPC7D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPD7D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPY26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPY6D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPY6C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BDC28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BB37D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BA37D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BA7DD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BB7DD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS38O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOC3O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YMCVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LMS9O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNC3O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRCNO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PN37O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PN35O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRCOO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PN41O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VSCRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PN36O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLCPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTCGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLC1O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PNDCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BACGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YMCIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YM39O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLCMO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YMCXO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLC4O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YFCJO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VSCVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YMCJO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRCPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VSCTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YM34O</t>
   </si>
   <si>
     <t xml:space="preserve">Template MASTER para un bono (MVP). Completar una fila por instrumento.</t>
@@ -96,11 +384,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,21 +419,42 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -173,20 +483,40 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -199,32 +529,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MasterBono" displayName="MasterBono" ref="A1:H1" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:H1"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="codigo"/>
-    <tableColumn id="2" name="moneda"/>
-    <tableColumn id="3" name="fecha_emision"/>
-    <tableColumn id="4" name="fecha_vto"/>
-    <tableColumn id="5" name="cupon_anual"/>
-    <tableColumn id="6" name="frecuencia"/>
-    <tableColumn id="7" name="amortizacion_tipo"/>
-    <tableColumn id="8" name="valor_nominal"/>
-  </tableColumns>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -407,57 +712,60 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="8.2734375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I1048576"/>
+  <sheetFormatPr defaultColWidth="8.21875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="1" style="1" width="20.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="15.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="2" width="15.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="15.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="6" style="1" width="15.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="8.22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>44081</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>47673</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <f aca="false">+0.75/100</f>
-        <v>0.0075</v>
+      <c r="C2" s="2" t="n">
+        <v>38680</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>50770</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0.0177</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>2</v>
@@ -469,25 +777,24 @@
         <v>100</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>44084</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>49499</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <f aca="false">+4.13/100</f>
-        <v>0.0413</v>
+      <c r="C3" s="2" t="n">
+        <v>37986</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>48944</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.0583</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>2</v>
@@ -499,39 +806,2686 @@
         <v>100</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="2" t="n">
+        <v>37986</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>53327</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.0331</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>40177</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>50770</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>44081</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D6" s="2" t="n">
+        <v>47308</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>47308</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>47452</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>47452</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>47673</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>47673</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>49499</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>49499</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>50414</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>50414</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D16" s="2" t="n">
         <v>51691</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <f aca="false">+3.5/100</f>
+      <c r="E16" s="3" t="n">
         <v>0.035</v>
       </c>
-      <c r="F4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>100</v>
-      </c>
-    </row>
+      <c r="F16" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>51691</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>47308</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>47308</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>47673</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I20" s="1" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>47673</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>49499</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I22" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>49499</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>49499</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>49499</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I25" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>51691</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I26" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>51691</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I27" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>53517</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I28" s="1" t="n">
+        <v>93.18</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>44081</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>53517</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>93.18</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>42660</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>46313</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I30" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>47633</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I31" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>44078</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>46335</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I32" s="1" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>47066</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I33" s="1" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>44712</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>48182</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F34" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I34" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I35" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I36" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I37" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>45323</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>46934</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I38" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>45366</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>46371</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I39" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>45366</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>46736</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I40" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>45412</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I41" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>45429</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>46477</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I42" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>45596</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>46325</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I43" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>45350</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I44" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I45" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>45296</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>46691</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F46" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H46" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I46" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>45596</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>46691</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F47" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H47" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I47" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>46691</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F48" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I48" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>45352</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>46691</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F49" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H49" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I49" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>46691</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F50" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H50" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I50" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>46691</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F51" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H51" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I51" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>46691</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F52" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H52" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I52" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>46691</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F53" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H53" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I53" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>46691</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F54" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H54" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I54" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>46691</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F55" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H55" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I55" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>46691</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F56" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H56" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I56" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>46691</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F57" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H57" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I57" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F58" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H58" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I58" s="1" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F59" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H59" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I59" s="1" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F60" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H60" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I60" s="1" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>46805</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="F61" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H61" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I61" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>48397</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="F62" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H62" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I62" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>50284</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H63" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I63" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>50284</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H64" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I64" s="1" t="n">
+        <v>91.84</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>50284</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="F65" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H65" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I65" s="1" t="n">
+        <v>91.84</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>50284</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="F66" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H66" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I66" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F67" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I67" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0.0749</v>
+      </c>
+      <c r="F68" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H68" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I68" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F69" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H69" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I69" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F70" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H70" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I70" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>46348</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="F71" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H71" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I71" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>46683</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="F72" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H72" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I72" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>47070</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="F73" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H73" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I73" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>47388</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="F74" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H74" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I74" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>47414</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="F75" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I75" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>47357</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F76" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H76" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I76" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>48131</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0.0765</v>
+      </c>
+      <c r="F77" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H77" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I77" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="78" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>48165</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="F78" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H78" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I78" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>48727</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="F79" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H79" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I79" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0.1095</v>
+      </c>
+      <c r="F80" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H80" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I80" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>46221</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F81" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H81" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I81" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>46507</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0.0913</v>
+      </c>
+      <c r="F82" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H82" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I82" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="83" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>47292</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F83" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H83" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I83" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>47299</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F84" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H84" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I84" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="85" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>47686</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0.0875</v>
+      </c>
+      <c r="F85" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H85" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I85" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>48047</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="F86" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H86" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I86" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>48102</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0.0875</v>
+      </c>
+      <c r="F87" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H87" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I87" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>48364</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.085</v>
+      </c>
+      <c r="F88" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H88" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I88" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>48503</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0.0788</v>
+      </c>
+      <c r="F89" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H89" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I89" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>48740</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>0.085</v>
+      </c>
+      <c r="F90" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H90" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I90" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>48852</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="F91" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H91" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I91" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>49399</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F92" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H92" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I92" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>49653</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0.0763</v>
+      </c>
+      <c r="F93" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H93" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I93" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="94" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>48961</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>0.0875</v>
+      </c>
+      <c r="F94" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H94" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I94" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C95" s="1"/>
+    </row>
+    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C96" s="1"/>
+    </row>
+    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C97" s="1"/>
+    </row>
+    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C98" s="1"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C99" s="1"/>
+    </row>
+    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C100" s="1"/>
+    </row>
+    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C101" s="1"/>
+    </row>
+    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C102" s="1"/>
+    </row>
+    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C103" s="1"/>
+    </row>
+    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C104" s="1"/>
+    </row>
+    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C105" s="1"/>
+    </row>
+    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C106" s="1"/>
+    </row>
+    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C107" s="1"/>
+    </row>
+    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C108" s="1"/>
+    </row>
+    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C109" s="1"/>
+    </row>
+    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C110" s="1"/>
+    </row>
+    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C111" s="1"/>
+    </row>
+    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C112" s="1"/>
+    </row>
+    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C113" s="1"/>
+    </row>
+    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C114" s="1"/>
+    </row>
+    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C115" s="1"/>
+    </row>
+    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C116" s="1"/>
+    </row>
+    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C117" s="1"/>
+    </row>
+    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C118" s="1"/>
+    </row>
+    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C119" s="1"/>
+    </row>
+    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C120" s="1"/>
+    </row>
+    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C121" s="1"/>
+    </row>
+    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C122" s="1"/>
+    </row>
+    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C123" s="1"/>
+    </row>
+    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C124" s="1"/>
+    </row>
+    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C125" s="1"/>
+    </row>
+    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C126" s="1"/>
+    </row>
+    <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C127" s="1"/>
+    </row>
+    <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C128" s="1"/>
+    </row>
+    <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C129" s="1"/>
+    </row>
+    <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C130" s="1"/>
+    </row>
+    <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C131" s="1"/>
+    </row>
+    <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C132" s="1"/>
+    </row>
+    <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C133" s="1"/>
+    </row>
+    <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C134" s="1"/>
+    </row>
+    <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C135" s="1"/>
+    </row>
+    <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C136" s="1"/>
+    </row>
+    <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C137" s="1"/>
+    </row>
+    <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C138" s="1"/>
+    </row>
+    <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C139" s="1"/>
+    </row>
+    <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C140" s="1"/>
+    </row>
+    <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C141" s="1"/>
+    </row>
+    <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C142" s="1"/>
+    </row>
+    <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C143" s="1"/>
+    </row>
+    <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C144" s="1"/>
+    </row>
+    <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C145" s="1"/>
+    </row>
+    <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C146" s="1"/>
+    </row>
+    <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C147" s="1"/>
+    </row>
+    <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C148" s="1"/>
+    </row>
+    <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C149" s="1"/>
+    </row>
+    <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C150" s="1"/>
+    </row>
+    <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C151" s="1"/>
+    </row>
+    <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C152" s="1"/>
+    </row>
+    <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C153" s="1"/>
+    </row>
+    <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C154" s="1"/>
+    </row>
+    <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C155" s="1"/>
+    </row>
+    <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C156" s="1"/>
+    </row>
+    <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C157" s="1"/>
+    </row>
+    <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C158" s="1"/>
+    </row>
+    <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -540,9 +3494,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <tableParts>
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -552,51 +3503,51 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultColWidth="8.2734375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.21875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
+      <c r="A1" s="4" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>15</v>
+      <c r="A2" s="8" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>16</v>
+      <c r="A3" s="8" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>17</v>
+      <c r="A4" s="8" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>18</v>
+      <c r="A5" s="8" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>19</v>
+      <c r="A6" s="8" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>20</v>
+      <c r="A7" s="8" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
+      <c r="A8" s="8" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>22</v>
+      <c r="A9" s="8" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/data/SPR_BS_master.xlsx
+++ b/data/SPR_BS_master.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="120">
   <si>
     <t xml:space="preserve">codigo</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t xml:space="preserve">valor_residual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">moneda_precio</t>
   </si>
   <si>
     <t xml:space="preserve">PARP</t>
@@ -712,14 +715,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I1048576"/>
+  <dimension ref="A1:J1048576"/>
   <sheetFormatPr defaultColWidth="8.21875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="15.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="2" width="15.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="15.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="6" style="1" width="15.33"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="8.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="1" width="15.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="1" width="8.22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -750,13 +753,16 @@
       <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>38680</v>
@@ -771,21 +777,24 @@
         <v>2</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>37986</v>
@@ -800,7 +809,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3" s="1" t="n">
         <v>100</v>
@@ -808,13 +817,16 @@
       <c r="I3" s="1" t="n">
         <v>80</v>
       </c>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>37986</v>
@@ -829,21 +841,24 @@
         <v>2</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>40177</v>
@@ -858,21 +873,24 @@
         <v>2</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I5" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>44081</v>
@@ -887,7 +905,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H6" s="1" t="n">
         <v>100</v>
@@ -895,13 +913,16 @@
       <c r="I6" s="1" t="n">
         <v>70</v>
       </c>
+      <c r="J6" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>44081</v>
@@ -916,7 +937,7 @@
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>100</v>
@@ -924,13 +945,16 @@
       <c r="I7" s="1" t="n">
         <v>70</v>
       </c>
+      <c r="J7" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>46007</v>
@@ -945,21 +969,24 @@
         <v>2</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I8" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>44081</v>
@@ -974,21 +1001,24 @@
         <v>2</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I9" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>44081</v>
@@ -1003,7 +1033,7 @@
         <v>2</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>100</v>
@@ -1011,13 +1041,16 @@
       <c r="I10" s="1" t="n">
         <v>72</v>
       </c>
+      <c r="J10" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>44081</v>
@@ -1032,7 +1065,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>100</v>
@@ -1040,13 +1073,16 @@
       <c r="I11" s="1" t="n">
         <v>72</v>
       </c>
+      <c r="J11" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>44081</v>
@@ -1061,21 +1097,24 @@
         <v>2</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>44081</v>
@@ -1090,21 +1129,24 @@
         <v>2</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H13" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I13" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>44081</v>
@@ -1119,21 +1161,24 @@
         <v>2</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H14" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>44081</v>
@@ -1148,21 +1193,24 @@
         <v>2</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H15" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I15" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>44081</v>
@@ -1177,21 +1225,24 @@
         <v>2</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H16" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I16" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>44081</v>
@@ -1206,21 +1257,24 @@
         <v>2</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H17" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I17" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>44081</v>
@@ -1235,7 +1289,7 @@
         <v>2</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H18" s="1" t="n">
         <v>100</v>
@@ -1243,13 +1297,16 @@
       <c r="I18" s="1" t="n">
         <v>70</v>
       </c>
+      <c r="J18" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>44081</v>
@@ -1264,7 +1321,7 @@
         <v>2</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H19" s="1" t="n">
         <v>100</v>
@@ -1272,13 +1329,16 @@
       <c r="I19" s="1" t="n">
         <v>70</v>
       </c>
+      <c r="J19" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>44081</v>
@@ -1293,7 +1353,7 @@
         <v>2</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H20" s="1" t="n">
         <v>100</v>
@@ -1301,13 +1361,16 @@
       <c r="I20" s="1" t="n">
         <v>72</v>
       </c>
+      <c r="J20" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>44081</v>
@@ -1322,7 +1385,7 @@
         <v>2</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H21" s="1" t="n">
         <v>100</v>
@@ -1330,13 +1393,16 @@
       <c r="I21" s="1" t="n">
         <v>72</v>
       </c>
+      <c r="J21" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>44081</v>
@@ -1351,21 +1417,24 @@
         <v>2</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H22" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I22" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>44081</v>
@@ -1380,21 +1449,24 @@
         <v>2</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H23" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I23" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>44081</v>
@@ -1409,21 +1481,24 @@
         <v>2</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H24" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I24" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>44081</v>
@@ -1438,21 +1513,24 @@
         <v>2</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H25" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I25" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>44081</v>
@@ -1467,21 +1545,24 @@
         <v>2</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H26" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I26" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>44081</v>
@@ -1496,21 +1577,24 @@
         <v>2</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H27" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I27" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>44081</v>
@@ -1525,7 +1609,7 @@
         <v>2</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H28" s="1" t="n">
         <v>100</v>
@@ -1533,13 +1617,16 @@
       <c r="I28" s="1" t="n">
         <v>93.18</v>
       </c>
+      <c r="J28" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>44081</v>
@@ -1554,7 +1641,7 @@
         <v>2</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H29" s="1" t="n">
         <v>100</v>
@@ -1562,13 +1649,16 @@
       <c r="I29" s="1" t="n">
         <v>93.18</v>
       </c>
+      <c r="J29" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>42660</v>
@@ -1583,21 +1673,24 @@
         <v>2</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H30" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I30" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>47633</v>
@@ -1609,21 +1702,24 @@
         <v>2</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H31" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I31" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>44078</v>
@@ -1638,7 +1734,7 @@
         <v>2</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H32" s="1" t="n">
         <v>100</v>
@@ -1646,13 +1742,16 @@
       <c r="I32" s="1" t="n">
         <v>40</v>
       </c>
+      <c r="J32" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>47066</v>
@@ -1664,7 +1763,7 @@
         <v>2</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H33" s="1" t="n">
         <v>100</v>
@@ -1672,13 +1771,16 @@
       <c r="I33" s="1" t="n">
         <v>60</v>
       </c>
+      <c r="J33" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>44712</v>
@@ -1693,21 +1795,24 @@
         <v>2</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H34" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I34" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>46203</v>
@@ -1719,21 +1824,24 @@
         <v>0</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H35" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I35" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>46234</v>
@@ -1745,21 +1853,24 @@
         <v>0</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H36" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I36" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>46568</v>
@@ -1771,21 +1882,24 @@
         <v>0</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H37" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I37" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>45323</v>
@@ -1800,21 +1914,24 @@
         <v>0</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H38" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I38" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>45366</v>
@@ -1829,21 +1946,24 @@
         <v>0</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H39" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I39" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>45366</v>
@@ -1858,21 +1978,24 @@
         <v>0</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H40" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I40" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>45412</v>
@@ -1887,21 +2010,24 @@
         <v>0</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H41" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I41" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>45429</v>
@@ -1916,21 +2042,24 @@
         <v>0</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H42" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I42" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>45596</v>
@@ -1945,21 +2074,24 @@
         <v>0</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H43" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I43" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>45350</v>
@@ -1974,21 +2106,24 @@
         <v>0</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H44" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I44" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>46142</v>
@@ -2000,21 +2135,24 @@
         <v>0</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H45" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I45" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>45296</v>
@@ -2029,21 +2167,24 @@
         <v>2</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H46" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I46" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>45596</v>
@@ -2058,21 +2199,24 @@
         <v>2</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H47" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I47" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>46691</v>
@@ -2084,21 +2228,24 @@
         <v>2</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H48" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I48" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>45352</v>
@@ -2113,21 +2260,24 @@
         <v>2</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H49" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I49" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>46691</v>
@@ -2139,21 +2289,24 @@
         <v>2</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H50" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I50" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>46691</v>
@@ -2165,21 +2318,24 @@
         <v>2</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H51" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I51" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>46691</v>
@@ -2191,21 +2347,24 @@
         <v>2</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H52" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I52" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>46691</v>
@@ -2217,21 +2376,24 @@
         <v>2</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H53" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I53" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>46691</v>
@@ -2243,21 +2405,24 @@
         <v>2</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H54" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I54" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="D55" s="2" t="n">
         <v>46691</v>
@@ -2269,21 +2434,24 @@
         <v>2</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H55" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I55" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>46691</v>
@@ -2295,21 +2463,24 @@
         <v>2</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H56" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I56" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>46691</v>
@@ -2321,21 +2492,24 @@
         <v>2</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H57" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I57" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D58" s="2" t="n">
         <v>46173</v>
@@ -2347,7 +2521,7 @@
         <v>4</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H58" s="1" t="n">
         <v>100</v>
@@ -2355,13 +2529,16 @@
       <c r="I58" s="1" t="n">
         <v>67</v>
       </c>
+      <c r="J58" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D59" s="2" t="n">
         <v>46173</v>
@@ -2373,7 +2550,7 @@
         <v>4</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H59" s="1" t="n">
         <v>100</v>
@@ -2381,13 +2558,16 @@
       <c r="I59" s="1" t="n">
         <v>67</v>
       </c>
+      <c r="J59" s="1" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D60" s="2" t="n">
         <v>46173</v>
@@ -2399,7 +2579,7 @@
         <v>4</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H60" s="1" t="n">
         <v>100</v>
@@ -2407,13 +2587,16 @@
       <c r="I60" s="1" t="n">
         <v>67</v>
       </c>
+      <c r="J60" s="1" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D61" s="2" t="n">
         <v>46805</v>
@@ -2425,21 +2608,24 @@
         <v>4</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H61" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I61" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D62" s="2" t="n">
         <v>48397</v>
@@ -2451,21 +2637,24 @@
         <v>2</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H62" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I62" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D63" s="2" t="n">
         <v>50284</v>
@@ -2477,21 +2666,24 @@
         <v>2</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H63" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I63" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D64" s="2" t="n">
         <v>50284</v>
@@ -2503,7 +2695,7 @@
         <v>2</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H64" s="1" t="n">
         <v>100</v>
@@ -2511,13 +2703,16 @@
       <c r="I64" s="1" t="n">
         <v>91.84</v>
       </c>
+      <c r="J64" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D65" s="2" t="n">
         <v>50284</v>
@@ -2529,7 +2724,7 @@
         <v>2</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H65" s="1" t="n">
         <v>100</v>
@@ -2537,13 +2732,16 @@
       <c r="I65" s="1" t="n">
         <v>91.84</v>
       </c>
+      <c r="J65" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D66" s="2" t="n">
         <v>50284</v>
@@ -2555,21 +2753,24 @@
         <v>2</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H66" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I66" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>46084</v>
@@ -2581,21 +2782,24 @@
         <v>2</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H67" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I67" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D68" s="2" t="n">
         <v>46092</v>
@@ -2607,21 +2811,24 @@
         <v>2</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H68" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I68" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D69" s="2" t="n">
         <v>46170</v>
@@ -2633,21 +2840,24 @@
         <v>4</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H69" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I69" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D70" s="2" t="n">
         <v>46186</v>
@@ -2659,21 +2869,24 @@
         <v>4</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H70" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I70" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D71" s="2" t="n">
         <v>46348</v>
@@ -2685,21 +2898,24 @@
         <v>2</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H71" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I71" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D72" s="2" t="n">
         <v>46683</v>
@@ -2711,21 +2927,24 @@
         <v>2</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H72" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I72" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>47070</v>
@@ -2737,21 +2956,24 @@
         <v>2</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H73" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I73" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D74" s="2" t="n">
         <v>47388</v>
@@ -2763,21 +2985,24 @@
         <v>2</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H74" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I74" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D75" s="2" t="n">
         <v>47414</v>
@@ -2789,21 +3014,24 @@
         <v>2</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H75" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I75" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D76" s="2" t="n">
         <v>47357</v>
@@ -2815,21 +3043,24 @@
         <v>2</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H76" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I76" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D77" s="2" t="n">
         <v>48131</v>
@@ -2841,21 +3072,24 @@
         <v>2</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H77" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I77" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D78" s="2" t="n">
         <v>48165</v>
@@ -2867,21 +3101,24 @@
         <v>2</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H78" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I78" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="79" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D79" s="2" t="n">
         <v>48727</v>
@@ -2893,21 +3130,24 @@
         <v>2</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H79" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I79" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="80" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D80" s="2" t="n">
         <v>46203</v>
@@ -2919,21 +3159,24 @@
         <v>4</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H80" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I80" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="81" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>46221</v>
@@ -2945,21 +3188,24 @@
         <v>2</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H81" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I81" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="82" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D82" s="2" t="n">
         <v>46507</v>
@@ -2971,21 +3217,24 @@
         <v>2</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H82" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I82" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="83" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D83" s="2" t="n">
         <v>47292</v>
@@ -2997,21 +3246,24 @@
         <v>2</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H83" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I83" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="84" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D84" s="2" t="n">
         <v>47299</v>
@@ -3023,21 +3275,24 @@
         <v>2</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H84" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I84" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="85" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D85" s="2" t="n">
         <v>47686</v>
@@ -3049,21 +3304,24 @@
         <v>2</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H85" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I85" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D86" s="2" t="n">
         <v>48047</v>
@@ -3075,21 +3333,24 @@
         <v>2</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H86" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I86" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="87" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D87" s="2" t="n">
         <v>48102</v>
@@ -3101,21 +3362,24 @@
         <v>2</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H87" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I87" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D88" s="2" t="n">
         <v>48364</v>
@@ -3127,21 +3391,24 @@
         <v>2</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H88" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I88" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D89" s="2" t="n">
         <v>48503</v>
@@ -3153,21 +3420,24 @@
         <v>2</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H89" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I89" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D90" s="2" t="n">
         <v>48740</v>
@@ -3179,21 +3449,24 @@
         <v>2</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H90" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I90" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D91" s="2" t="n">
         <v>48852</v>
@@ -3205,21 +3478,24 @@
         <v>2</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H91" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I91" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D92" s="2" t="n">
         <v>49399</v>
@@ -3231,21 +3507,24 @@
         <v>2</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H92" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I92" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="93" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D93" s="2" t="n">
         <v>49653</v>
@@ -3257,21 +3536,24 @@
         <v>2</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H93" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I93" s="1" t="n">
         <v>100</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D94" s="2" t="n">
         <v>48961</v>
@@ -3283,7 +3565,7 @@
         <v>2</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H94" s="1" t="n">
         <v>100</v>
@@ -3291,197 +3573,200 @@
       <c r="I94" s="1" t="n">
         <v>100</v>
       </c>
-    </row>
-    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J94" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C95" s="1"/>
     </row>
-    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C96" s="1"/>
     </row>
-    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C97" s="1"/>
     </row>
-    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C98" s="1"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C99" s="1"/>
     </row>
-    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C100" s="1"/>
     </row>
-    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C101" s="1"/>
     </row>
-    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C102" s="1"/>
     </row>
-    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C103" s="1"/>
     </row>
-    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C104" s="1"/>
     </row>
-    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C105" s="1"/>
     </row>
-    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C106" s="1"/>
     </row>
-    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C107" s="1"/>
     </row>
-    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C108" s="1"/>
     </row>
-    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C109" s="1"/>
     </row>
-    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C110" s="1"/>
     </row>
-    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C111" s="1"/>
     </row>
-    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C112" s="1"/>
     </row>
-    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C113" s="1"/>
     </row>
-    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C114" s="1"/>
     </row>
-    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C115" s="1"/>
     </row>
-    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C116" s="1"/>
     </row>
-    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C117" s="1"/>
     </row>
-    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C118" s="1"/>
     </row>
-    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C119" s="1"/>
     </row>
-    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C120" s="1"/>
     </row>
-    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C121" s="1"/>
     </row>
-    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C122" s="1"/>
     </row>
-    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C123" s="1"/>
     </row>
-    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C124" s="1"/>
     </row>
-    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C125" s="1"/>
     </row>
-    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C126" s="1"/>
     </row>
-    <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C127" s="1"/>
     </row>
-    <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C128" s="1"/>
     </row>
-    <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C129" s="1"/>
     </row>
-    <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C130" s="1"/>
     </row>
-    <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C131" s="1"/>
     </row>
-    <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C132" s="1"/>
     </row>
-    <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C133" s="1"/>
     </row>
-    <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C134" s="1"/>
     </row>
-    <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C135" s="1"/>
     </row>
-    <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C136" s="1"/>
     </row>
-    <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C137" s="1"/>
     </row>
-    <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C138" s="1"/>
     </row>
-    <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C139" s="1"/>
     </row>
-    <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C140" s="1"/>
     </row>
-    <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C141" s="1"/>
     </row>
-    <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C142" s="1"/>
     </row>
-    <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C143" s="1"/>
     </row>
-    <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C144" s="1"/>
     </row>
-    <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C145" s="1"/>
     </row>
-    <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C146" s="1"/>
     </row>
-    <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C147" s="1"/>
     </row>
-    <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C148" s="1"/>
     </row>
-    <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C149" s="1"/>
     </row>
-    <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C150" s="1"/>
     </row>
-    <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C151" s="1"/>
     </row>
-    <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C152" s="1"/>
     </row>
-    <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C153" s="1"/>
     </row>
-    <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C154" s="1"/>
     </row>
-    <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C155" s="1"/>
     </row>
-    <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C156" s="1"/>
     </row>
-    <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C157" s="1"/>
     </row>
-    <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C158" s="1"/>
     </row>
     <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3507,47 +3792,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/data/SPR_BS_master.xlsx
+++ b/data/SPR_BS_master.xlsx
@@ -1,18 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\SPR-BS\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E862E4-E0E7-4FC5-9BA4-5091DFF1445C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="master_bono" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="README" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="master_bono" sheetId="1" r:id="rId1"/>
+    <sheet name="README" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="true" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -21,378 +37,386 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="120">
-  <si>
-    <t xml:space="preserve">codigo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">moneda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fecha_emision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fecha_vto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cupon_anual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">frecuencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amortizacion_tipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valor_nominal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valor_residual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">moneda_precio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parcial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DICP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAP0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL29D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AN29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bullet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AN29D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL30D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL35D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AE38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AE38D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL41D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GD29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GD29D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GD30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GD30D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GD35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GD35D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GD38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GD38D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GD41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GD41D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GD46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GD46D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TO26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TY30P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TX26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARS CER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TX28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TX31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TZX26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X31L6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TZX27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TZX28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TZXD6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TZXD7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TZXM6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TZXM7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TZXO6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TZV26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARS USD LINKED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D30A6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPOA7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPOB7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPOC7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPOD7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPA7C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USD CCL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPB7C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPC7C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPD7C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPA7D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USD MEP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPB7D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPC7D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPD7D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPY26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPY6D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPY6C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BDC28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CO32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BB37D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BA37D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BA7DD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BB7DD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS38O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOC3O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YMCVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LMS9O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNC3O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRCNO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PN37O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PN35O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRCOO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PN41O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VSCRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PN36O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLCPO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTCGO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLC1O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PNDCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BACGO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YMCIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YM39O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLCMO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YMCXO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLC4O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YFCJO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VSCVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YMCJO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRCPO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VSCTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YM34O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Template MASTER para un bono (MVP). Completar una fila por instrumento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campos:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">codigo: ticker (ej AL30)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">moneda: USD o ARS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fecha_emision / fecha_vto: formato YYYY-MM-DD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cupon_anual: tasa anual en decimal (ej 0.01 = 1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">frecuencia: pagos por año (2 = semestral)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amortizacion_tipo: bullet | parcial | escalonada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valor_nominal: normalmente 100</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="123">
+  <si>
+    <t>codigo</t>
+  </si>
+  <si>
+    <t>moneda</t>
+  </si>
+  <si>
+    <t>fecha_emision</t>
+  </si>
+  <si>
+    <t>fecha_vto</t>
+  </si>
+  <si>
+    <t>cupon_anual</t>
+  </si>
+  <si>
+    <t>frecuencia</t>
+  </si>
+  <si>
+    <t>amortizacion_tipo</t>
+  </si>
+  <si>
+    <t>valor_nominal</t>
+  </si>
+  <si>
+    <t>valor_residual</t>
+  </si>
+  <si>
+    <t>moneda_precio</t>
+  </si>
+  <si>
+    <t>PARP</t>
+  </si>
+  <si>
+    <t>ARS</t>
+  </si>
+  <si>
+    <t>parcial</t>
+  </si>
+  <si>
+    <t>DICP</t>
+  </si>
+  <si>
+    <t>CUAP</t>
+  </si>
+  <si>
+    <t>PAP0</t>
+  </si>
+  <si>
+    <t>AL29</t>
+  </si>
+  <si>
+    <t>AL29D</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>AN29</t>
+  </si>
+  <si>
+    <t>bullet</t>
+  </si>
+  <si>
+    <t>AN29D</t>
+  </si>
+  <si>
+    <t>AL30</t>
+  </si>
+  <si>
+    <t>AL30D</t>
+  </si>
+  <si>
+    <t>AL35</t>
+  </si>
+  <si>
+    <t>AL35D</t>
+  </si>
+  <si>
+    <t>AE38</t>
+  </si>
+  <si>
+    <t>AE38D</t>
+  </si>
+  <si>
+    <t>AL41</t>
+  </si>
+  <si>
+    <t>AL41D</t>
+  </si>
+  <si>
+    <t>GD29</t>
+  </si>
+  <si>
+    <t>GD29D</t>
+  </si>
+  <si>
+    <t>GD30</t>
+  </si>
+  <si>
+    <t>GD30D</t>
+  </si>
+  <si>
+    <t>GD35</t>
+  </si>
+  <si>
+    <t>GD35D</t>
+  </si>
+  <si>
+    <t>GD38</t>
+  </si>
+  <si>
+    <t>GD38D</t>
+  </si>
+  <si>
+    <t>GD41</t>
+  </si>
+  <si>
+    <t>GD41D</t>
+  </si>
+  <si>
+    <t>GD46</t>
+  </si>
+  <si>
+    <t>GD46D</t>
+  </si>
+  <si>
+    <t>TO26</t>
+  </si>
+  <si>
+    <t>TY30P</t>
+  </si>
+  <si>
+    <t>TX26</t>
+  </si>
+  <si>
+    <t>ARS CER</t>
+  </si>
+  <si>
+    <t>TX28</t>
+  </si>
+  <si>
+    <t>TX31</t>
+  </si>
+  <si>
+    <t>TZX26</t>
+  </si>
+  <si>
+    <t>X31L6</t>
+  </si>
+  <si>
+    <t>TZX27</t>
+  </si>
+  <si>
+    <t>TZX28</t>
+  </si>
+  <si>
+    <t>TZXD6</t>
+  </si>
+  <si>
+    <t>TZXD7</t>
+  </si>
+  <si>
+    <t>TZXM6</t>
+  </si>
+  <si>
+    <t>TZXM7</t>
+  </si>
+  <si>
+    <t>TZXO6</t>
+  </si>
+  <si>
+    <t>TZV26</t>
+  </si>
+  <si>
+    <t>ARS USD LINKED</t>
+  </si>
+  <si>
+    <t>D30A6</t>
+  </si>
+  <si>
+    <t>BPOA7</t>
+  </si>
+  <si>
+    <t>BPOB7</t>
+  </si>
+  <si>
+    <t>BPOC7</t>
+  </si>
+  <si>
+    <t>BPOD7</t>
+  </si>
+  <si>
+    <t>BPA7C</t>
+  </si>
+  <si>
+    <t>USD CCL</t>
+  </si>
+  <si>
+    <t>BPB7C</t>
+  </si>
+  <si>
+    <t>BPC7C</t>
+  </si>
+  <si>
+    <t>BPD7C</t>
+  </si>
+  <si>
+    <t>BPA7D</t>
+  </si>
+  <si>
+    <t>USD MEP</t>
+  </si>
+  <si>
+    <t>BPB7D</t>
+  </si>
+  <si>
+    <t>BPC7D</t>
+  </si>
+  <si>
+    <t>BPD7D</t>
+  </si>
+  <si>
+    <t>BPY26</t>
+  </si>
+  <si>
+    <t>BPY6D</t>
+  </si>
+  <si>
+    <t>BPY6C</t>
+  </si>
+  <si>
+    <t>BDC28</t>
+  </si>
+  <si>
+    <t>CO32</t>
+  </si>
+  <si>
+    <t>BB37D</t>
+  </si>
+  <si>
+    <t>BA37D</t>
+  </si>
+  <si>
+    <t>BA7DD</t>
+  </si>
+  <si>
+    <t>BB7DD</t>
+  </si>
+  <si>
+    <t>CS38O</t>
+  </si>
+  <si>
+    <t>LOC3O</t>
+  </si>
+  <si>
+    <t>YMCVO</t>
+  </si>
+  <si>
+    <t>LMS9O</t>
+  </si>
+  <si>
+    <t>DNC3O</t>
+  </si>
+  <si>
+    <t>IRCNO</t>
+  </si>
+  <si>
+    <t>PN37O</t>
+  </si>
+  <si>
+    <t>PN35O</t>
+  </si>
+  <si>
+    <t>IRCOO</t>
+  </si>
+  <si>
+    <t>PN41O</t>
+  </si>
+  <si>
+    <t>VSCRO</t>
+  </si>
+  <si>
+    <t>PN36O</t>
+  </si>
+  <si>
+    <t>TLCPO</t>
+  </si>
+  <si>
+    <t>MTCGO</t>
+  </si>
+  <si>
+    <t>TLC1O</t>
+  </si>
+  <si>
+    <t>PNDCO</t>
+  </si>
+  <si>
+    <t>BACGO</t>
+  </si>
+  <si>
+    <t>YMCIO</t>
+  </si>
+  <si>
+    <t>YM39O</t>
+  </si>
+  <si>
+    <t>TLCMO</t>
+  </si>
+  <si>
+    <t>YMCXO</t>
+  </si>
+  <si>
+    <t>PLC4O</t>
+  </si>
+  <si>
+    <t>YFCJO</t>
+  </si>
+  <si>
+    <t>VSCVO</t>
+  </si>
+  <si>
+    <t>YMCJO</t>
+  </si>
+  <si>
+    <t>IRCPO</t>
+  </si>
+  <si>
+    <t>VSCTO</t>
+  </si>
+  <si>
+    <t>YM34O</t>
+  </si>
+  <si>
+    <t>Template MASTER para un bono (MVP). Completar una fila por instrumento.</t>
+  </si>
+  <si>
+    <t>Campos:</t>
+  </si>
+  <si>
+    <t>codigo: ticker (ej AL30)</t>
+  </si>
+  <si>
+    <t>moneda: USD o ARS</t>
+  </si>
+  <si>
+    <t>fecha_emision / fecha_vto: formato YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t>cupon_anual: tasa anual en decimal (ej 0.01 = 1%)</t>
+  </si>
+  <si>
+    <t>frecuencia: pagos por año (2 = semestral)</t>
+  </si>
+  <si>
+    <t>amortizacion_tipo: bullet | parcial | escalonada</t>
+  </si>
+  <si>
+    <t>valor_nominal: normalmente 100</t>
+  </si>
+  <si>
+    <t>tipo_instrumento</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>SOBERANO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -401,29 +425,13 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <name val="Cambria"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -446,131 +454,108 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -578,12 +563,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -612,7 +597,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -633,7 +618,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -684,7 +669,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -702,30 +687,29 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:J1048576"/>
-  <sheetFormatPr defaultColWidth="8.21875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K1048576"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="15.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="2" width="15.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="15.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="1" width="15.33"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="1" width="8.22"/>
+    <col min="1" max="2" width="15.33203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" style="3" customWidth="1"/>
+    <col min="6" max="11" width="15.33203125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.21875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -756,3092 +740,3379 @@
       <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="2">
         <v>38680</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="2">
         <v>50770</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>0.0177</v>
-      </c>
-      <c r="F2" s="1" t="n">
+      <c r="E2" s="3">
+        <v>1.77E-2</v>
+      </c>
+      <c r="F2" s="1">
         <v>2</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I2" s="1" t="n">
+      <c r="H2" s="1">
+        <v>100</v>
+      </c>
+      <c r="I2" s="1">
         <v>100</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K2" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="2">
         <v>37986</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="2">
         <v>48944</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>0.0583</v>
-      </c>
-      <c r="F3" s="1" t="n">
+      <c r="E3" s="3">
+        <v>5.8299999999999998E-2</v>
+      </c>
+      <c r="F3" s="1">
         <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I3" s="1" t="n">
+      <c r="H3" s="1">
+        <v>100</v>
+      </c>
+      <c r="I3" s="1">
         <v>80</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K3" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="2">
         <v>37986</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="2">
         <v>53327</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>0.0331</v>
-      </c>
-      <c r="F4" s="1" t="n">
+      <c r="E4" s="3">
+        <v>3.3099999999999997E-2</v>
+      </c>
+      <c r="F4" s="1">
         <v>2</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I4" s="1" t="n">
+      <c r="H4" s="1">
+        <v>100</v>
+      </c>
+      <c r="I4" s="1">
         <v>100</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K4" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="2">
         <v>40177</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="2">
         <v>50770</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>0.0177</v>
-      </c>
-      <c r="F5" s="1" t="n">
+      <c r="E5" s="3">
+        <v>1.77E-2</v>
+      </c>
+      <c r="F5" s="1">
         <v>2</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I5" s="1" t="n">
+      <c r="H5" s="1">
+        <v>100</v>
+      </c>
+      <c r="I5" s="1">
         <v>100</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K5" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="2">
         <v>44081</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="2">
         <v>47308</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="3">
         <v>0.01</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="1">
         <v>2</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I6" s="1" t="n">
+      <c r="H6" s="1">
+        <v>100</v>
+      </c>
+      <c r="I6" s="1">
         <v>70</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K6" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="2">
         <v>44081</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="2">
         <v>47308</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="3">
         <v>0.01</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I7" s="1" t="n">
+      <c r="H7" s="1">
+        <v>100</v>
+      </c>
+      <c r="I7" s="1">
         <v>70</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K7" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="2">
         <v>46007</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="2">
         <v>47452</v>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="F8" s="1" t="n">
+      <c r="E8" s="3">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="F8" s="1">
         <v>2</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I8" s="1" t="n">
+      <c r="H8" s="1">
+        <v>100</v>
+      </c>
+      <c r="I8" s="1">
         <v>100</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K8" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="2">
         <v>44081</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="2">
         <v>47452</v>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="F9" s="1" t="n">
+      <c r="E9" s="3">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="F9" s="1">
         <v>2</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I9" s="1" t="n">
+      <c r="H9" s="1">
+        <v>100</v>
+      </c>
+      <c r="I9" s="1">
         <v>100</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K9" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="2">
         <v>44081</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="2">
         <v>47673</v>
       </c>
-      <c r="E10" s="3" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="F10" s="1" t="n">
+      <c r="E10" s="3">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="F10" s="1">
         <v>2</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I10" s="1" t="n">
+      <c r="H10" s="1">
+        <v>100</v>
+      </c>
+      <c r="I10" s="1">
         <v>72</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K10" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="2">
         <v>44081</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="2">
         <v>47673</v>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="F11" s="1" t="n">
+      <c r="E11" s="3">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="F11" s="1">
         <v>2</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I11" s="1" t="n">
+      <c r="H11" s="1">
+        <v>100</v>
+      </c>
+      <c r="I11" s="1">
         <v>72</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K11" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" s="2">
         <v>44081</v>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="2">
         <v>49499</v>
       </c>
-      <c r="E12" s="3" t="n">
-        <v>0.0413</v>
-      </c>
-      <c r="F12" s="1" t="n">
+      <c r="E12" s="3">
+        <v>4.1300000000000003E-2</v>
+      </c>
+      <c r="F12" s="1">
         <v>2</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I12" s="1" t="n">
+      <c r="H12" s="1">
+        <v>100</v>
+      </c>
+      <c r="I12" s="1">
         <v>100</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K12" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" s="2">
         <v>44081</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="2">
         <v>49499</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>0.0413</v>
-      </c>
-      <c r="F13" s="1" t="n">
+      <c r="E13" s="3">
+        <v>4.1300000000000003E-2</v>
+      </c>
+      <c r="F13" s="1">
         <v>2</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H13" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I13" s="1" t="n">
+      <c r="H13" s="1">
+        <v>100</v>
+      </c>
+      <c r="I13" s="1">
         <v>100</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K13" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" s="2">
         <v>44081</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="2">
         <v>50414</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="3">
         <v>0.05</v>
       </c>
-      <c r="F14" s="1" t="n">
+      <c r="F14" s="1">
         <v>2</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H14" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I14" s="1" t="n">
+      <c r="H14" s="1">
+        <v>100</v>
+      </c>
+      <c r="I14" s="1">
         <v>100</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K14" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C15" s="2">
         <v>44081</v>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="2">
         <v>50414</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="3">
         <v>0.05</v>
       </c>
-      <c r="F15" s="1" t="n">
+      <c r="F15" s="1">
         <v>2</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H15" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I15" s="1" t="n">
+      <c r="H15" s="1">
+        <v>100</v>
+      </c>
+      <c r="I15" s="1">
         <v>100</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K15" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C16" s="2">
         <v>44081</v>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" s="2">
         <v>51691</v>
       </c>
-      <c r="E16" s="3" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="F16" s="1" t="n">
+      <c r="E16" s="3">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="F16" s="1">
         <v>2</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H16" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I16" s="1" t="n">
+      <c r="H16" s="1">
+        <v>100</v>
+      </c>
+      <c r="I16" s="1">
         <v>100</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K16" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C17" s="2">
         <v>44081</v>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="2">
         <v>51691</v>
       </c>
-      <c r="E17" s="3" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="F17" s="1" t="n">
+      <c r="E17" s="3">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="F17" s="1">
         <v>2</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H17" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I17" s="1" t="n">
+      <c r="H17" s="1">
+        <v>100</v>
+      </c>
+      <c r="I17" s="1">
         <v>100</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K17" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C18" s="2">
         <v>44081</v>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="2">
         <v>47308</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="3">
         <v>0.01</v>
       </c>
-      <c r="F18" s="1" t="n">
+      <c r="F18" s="1">
         <v>2</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H18" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I18" s="1" t="n">
+      <c r="H18" s="1">
+        <v>100</v>
+      </c>
+      <c r="I18" s="1">
         <v>70</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K18" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>31</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="C19" s="2">
         <v>44081</v>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" s="2">
         <v>47308</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="3">
         <v>0.01</v>
       </c>
-      <c r="F19" s="1" t="n">
+      <c r="F19" s="1">
         <v>2</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H19" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I19" s="1" t="n">
+      <c r="H19" s="1">
+        <v>100</v>
+      </c>
+      <c r="I19" s="1">
         <v>70</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K19" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="C20" s="2">
         <v>44081</v>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D20" s="2">
         <v>47673</v>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="F20" s="1" t="n">
+      <c r="E20" s="3">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="F20" s="1">
         <v>2</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H20" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I20" s="1" t="n">
+      <c r="H20" s="1">
+        <v>100</v>
+      </c>
+      <c r="I20" s="1">
         <v>72</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K20" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="C21" s="2">
         <v>44081</v>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D21" s="2">
         <v>47673</v>
       </c>
-      <c r="E21" s="3" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="F21" s="1" t="n">
+      <c r="E21" s="3">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="F21" s="1">
         <v>2</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H21" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I21" s="1" t="n">
+      <c r="H21" s="1">
+        <v>100</v>
+      </c>
+      <c r="I21" s="1">
         <v>72</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K21" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="C22" s="2">
         <v>44081</v>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D22" s="2">
         <v>49499</v>
       </c>
-      <c r="E22" s="3" t="n">
-        <v>0.0413</v>
-      </c>
-      <c r="F22" s="1" t="n">
+      <c r="E22" s="3">
+        <v>4.1300000000000003E-2</v>
+      </c>
+      <c r="F22" s="1">
         <v>2</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H22" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I22" s="1" t="n">
+      <c r="H22" s="1">
+        <v>100</v>
+      </c>
+      <c r="I22" s="1">
         <v>100</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K22" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C23" s="2">
         <v>44081</v>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D23" s="2">
         <v>49499</v>
       </c>
-      <c r="E23" s="3" t="n">
-        <v>0.0413</v>
-      </c>
-      <c r="F23" s="1" t="n">
+      <c r="E23" s="3">
+        <v>4.1300000000000003E-2</v>
+      </c>
+      <c r="F23" s="1">
         <v>2</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H23" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I23" s="1" t="n">
+      <c r="H23" s="1">
+        <v>100</v>
+      </c>
+      <c r="I23" s="1">
         <v>100</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K23" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C24" s="2">
         <v>44081</v>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="2">
         <v>49499</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="3">
         <v>0.05</v>
       </c>
-      <c r="F24" s="1" t="n">
+      <c r="F24" s="1">
         <v>2</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H24" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I24" s="1" t="n">
+      <c r="H24" s="1">
+        <v>100</v>
+      </c>
+      <c r="I24" s="1">
         <v>100</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K24" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C25" s="2">
         <v>44081</v>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="2">
         <v>49499</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="3">
         <v>0.05</v>
       </c>
-      <c r="F25" s="1" t="n">
+      <c r="F25" s="1">
         <v>2</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H25" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I25" s="1" t="n">
+      <c r="H25" s="1">
+        <v>100</v>
+      </c>
+      <c r="I25" s="1">
         <v>100</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K25" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C26" s="2">
         <v>44081</v>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="2">
         <v>51691</v>
       </c>
-      <c r="E26" s="3" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="F26" s="1" t="n">
+      <c r="E26" s="3">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="F26" s="1">
         <v>2</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H26" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I26" s="1" t="n">
+      <c r="H26" s="1">
+        <v>100</v>
+      </c>
+      <c r="I26" s="1">
         <v>100</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K26" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="2" t="n">
+      <c r="C27" s="2">
         <v>44081</v>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="D27" s="2">
         <v>51691</v>
       </c>
-      <c r="E27" s="3" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="F27" s="1" t="n">
+      <c r="E27" s="3">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="F27" s="1">
         <v>2</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H27" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I27" s="1" t="n">
+      <c r="H27" s="1">
+        <v>100</v>
+      </c>
+      <c r="I27" s="1">
         <v>100</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K27" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="2" t="n">
+      <c r="C28" s="2">
         <v>44081</v>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D28" s="2">
         <v>53517</v>
       </c>
-      <c r="E28" s="3" t="n">
-        <v>0.0413</v>
-      </c>
-      <c r="F28" s="1" t="n">
+      <c r="E28" s="3">
+        <v>4.1300000000000003E-2</v>
+      </c>
+      <c r="F28" s="1">
         <v>2</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H28" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I28" s="1" t="n">
+      <c r="H28" s="1">
+        <v>100</v>
+      </c>
+      <c r="I28" s="1">
         <v>93.18</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K28" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C29" s="2">
         <v>44081</v>
       </c>
-      <c r="D29" s="2" t="n">
+      <c r="D29" s="2">
         <v>53517</v>
       </c>
-      <c r="E29" s="3" t="n">
-        <v>0.0413</v>
-      </c>
-      <c r="F29" s="1" t="n">
+      <c r="E29" s="3">
+        <v>4.1300000000000003E-2</v>
+      </c>
+      <c r="F29" s="1">
         <v>2</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H29" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I29" s="1" t="n">
+      <c r="H29" s="1">
+        <v>100</v>
+      </c>
+      <c r="I29" s="1">
         <v>93.18</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K29" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="2" t="n">
+      <c r="C30" s="2">
         <v>42660</v>
       </c>
-      <c r="D30" s="2" t="n">
+      <c r="D30" s="2">
         <v>46313</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="3">
         <v>0.155</v>
       </c>
-      <c r="F30" s="1" t="n">
+      <c r="F30" s="1">
         <v>2</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H30" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I30" s="1" t="n">
+      <c r="H30" s="1">
+        <v>100</v>
+      </c>
+      <c r="I30" s="1">
         <v>100</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K30" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="2" t="n">
+      <c r="D31" s="2">
         <v>47633</v>
       </c>
-      <c r="E31" s="3" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="F31" s="1" t="n">
+      <c r="E31" s="3">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="F31" s="1">
         <v>2</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H31" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I31" s="1" t="n">
+      <c r="H31" s="1">
+        <v>100</v>
+      </c>
+      <c r="I31" s="1">
         <v>100</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K31" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>44</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="2" t="n">
+      <c r="C32" s="2">
         <v>44078</v>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="D32" s="2">
         <v>46335</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="3">
         <v>0.02</v>
       </c>
-      <c r="F32" s="1" t="n">
+      <c r="F32" s="1">
         <v>2</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I32" s="1" t="n">
+      <c r="H32" s="1">
+        <v>100</v>
+      </c>
+      <c r="I32" s="1">
         <v>40</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K32" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D33" s="2" t="n">
+      <c r="D33" s="2">
         <v>47066</v>
       </c>
-      <c r="E33" s="3" t="n">
-        <v>0.0225</v>
-      </c>
-      <c r="F33" s="1" t="n">
+      <c r="E33" s="3">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="F33" s="1">
         <v>2</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H33" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I33" s="1" t="n">
+      <c r="H33" s="1">
+        <v>100</v>
+      </c>
+      <c r="I33" s="1">
         <v>60</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K33" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="2" t="n">
+      <c r="C34" s="2">
         <v>44712</v>
       </c>
-      <c r="D34" s="2" t="n">
+      <c r="D34" s="2">
         <v>48182</v>
       </c>
-      <c r="E34" s="3" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="F34" s="1" t="n">
+      <c r="E34" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="F34" s="1">
         <v>2</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H34" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I34" s="1" t="n">
+      <c r="H34" s="1">
+        <v>100</v>
+      </c>
+      <c r="I34" s="1">
         <v>100</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K34" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D35" s="2" t="n">
+      <c r="D35" s="2">
         <v>46203</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="3">
         <v>0</v>
       </c>
-      <c r="F35" s="1" t="n">
+      <c r="F35" s="1">
         <v>0</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H35" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I35" s="1" t="n">
+      <c r="H35" s="1">
+        <v>100</v>
+      </c>
+      <c r="I35" s="1">
         <v>100</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K35" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D36" s="2">
         <v>46234</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="3">
         <v>0</v>
       </c>
-      <c r="F36" s="1" t="n">
+      <c r="F36" s="1">
         <v>0</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H36" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I36" s="1" t="n">
+      <c r="H36" s="1">
+        <v>100</v>
+      </c>
+      <c r="I36" s="1">
         <v>100</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K36" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D37" s="2" t="n">
+      <c r="D37" s="2">
         <v>46568</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="3">
         <v>0</v>
       </c>
-      <c r="F37" s="1" t="n">
+      <c r="F37" s="1">
         <v>0</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H37" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I37" s="1" t="n">
+      <c r="H37" s="1">
+        <v>100</v>
+      </c>
+      <c r="I37" s="1">
         <v>100</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K37" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="2" t="n">
+      <c r="C38" s="2">
         <v>45323</v>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="D38" s="2">
         <v>46934</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="3">
         <v>0</v>
       </c>
-      <c r="F38" s="1" t="n">
+      <c r="F38" s="1">
         <v>0</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H38" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I38" s="1" t="n">
+      <c r="H38" s="1">
+        <v>100</v>
+      </c>
+      <c r="I38" s="1">
         <v>100</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K38" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C39" s="2" t="n">
+      <c r="C39" s="2">
         <v>45366</v>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="D39" s="2">
         <v>46371</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="3">
         <v>0</v>
       </c>
-      <c r="F39" s="1" t="n">
+      <c r="F39" s="1">
         <v>0</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H39" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I39" s="1" t="n">
+      <c r="H39" s="1">
+        <v>100</v>
+      </c>
+      <c r="I39" s="1">
         <v>100</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K39" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="2" t="n">
+      <c r="C40" s="2">
         <v>45366</v>
       </c>
-      <c r="D40" s="2" t="n">
+      <c r="D40" s="2">
         <v>46736</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="3">
         <v>0</v>
       </c>
-      <c r="F40" s="1" t="n">
+      <c r="F40" s="1">
         <v>0</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H40" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I40" s="1" t="n">
+      <c r="H40" s="1">
+        <v>100</v>
+      </c>
+      <c r="I40" s="1">
         <v>100</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K40" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C41" s="2" t="n">
+      <c r="C41" s="2">
         <v>45412</v>
       </c>
-      <c r="D41" s="2" t="n">
+      <c r="D41" s="2">
         <v>46112</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="3">
         <v>0</v>
       </c>
-      <c r="F41" s="1" t="n">
+      <c r="F41" s="1">
         <v>0</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H41" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I41" s="1" t="n">
+      <c r="H41" s="1">
+        <v>100</v>
+      </c>
+      <c r="I41" s="1">
         <v>100</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K41" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C42" s="2" t="n">
+      <c r="C42" s="2">
         <v>45429</v>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D42" s="2">
         <v>46477</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="3">
         <v>0</v>
       </c>
-      <c r="F42" s="1" t="n">
+      <c r="F42" s="1">
         <v>0</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H42" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I42" s="1" t="n">
+      <c r="H42" s="1">
+        <v>100</v>
+      </c>
+      <c r="I42" s="1">
         <v>100</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K42" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C43" s="2" t="n">
+      <c r="C43" s="2">
         <v>45596</v>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="D43" s="2">
         <v>46325</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="3">
         <v>0</v>
       </c>
-      <c r="F43" s="1" t="n">
+      <c r="F43" s="1">
         <v>0</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H43" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I43" s="1" t="n">
+      <c r="H43" s="1">
+        <v>100</v>
+      </c>
+      <c r="I43" s="1">
         <v>100</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K43" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="2" t="n">
+      <c r="C44" s="2">
         <v>45350</v>
       </c>
-      <c r="D44" s="2" t="n">
+      <c r="D44" s="2">
         <v>46203</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="3">
         <v>0</v>
       </c>
-      <c r="F44" s="1" t="n">
+      <c r="F44" s="1">
         <v>0</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H44" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I44" s="1" t="n">
+      <c r="H44" s="1">
+        <v>100</v>
+      </c>
+      <c r="I44" s="1">
         <v>100</v>
       </c>
       <c r="J44" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K44" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="D45" s="2">
         <v>46142</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="3">
         <v>0</v>
       </c>
-      <c r="F45" s="1" t="n">
+      <c r="F45" s="1">
         <v>0</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H45" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I45" s="1" t="n">
+      <c r="H45" s="1">
+        <v>100</v>
+      </c>
+      <c r="I45" s="1">
         <v>100</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K45" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>60</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C46" s="2" t="n">
+      <c r="C46" s="2">
         <v>45296</v>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="D46" s="2">
         <v>46691</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="3">
         <v>0.05</v>
       </c>
-      <c r="F46" s="1" t="n">
+      <c r="F46" s="1">
         <v>2</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H46" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I46" s="1" t="n">
+      <c r="H46" s="1">
+        <v>100</v>
+      </c>
+      <c r="I46" s="1">
         <v>100</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K46" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C47" s="2" t="n">
+      <c r="C47" s="2">
         <v>45596</v>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="D47" s="2">
         <v>46691</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="3">
         <v>0.05</v>
       </c>
-      <c r="F47" s="1" t="n">
+      <c r="F47" s="1">
         <v>2</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H47" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I47" s="1" t="n">
+      <c r="H47" s="1">
+        <v>100</v>
+      </c>
+      <c r="I47" s="1">
         <v>100</v>
       </c>
       <c r="J47" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K47" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D48" s="2">
         <v>46691</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="E48" s="3">
         <v>0.05</v>
       </c>
-      <c r="F48" s="1" t="n">
+      <c r="F48" s="1">
         <v>2</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H48" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I48" s="1" t="n">
+      <c r="H48" s="1">
+        <v>100</v>
+      </c>
+      <c r="I48" s="1">
         <v>100</v>
       </c>
       <c r="J48" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K48" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>63</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C49" s="2" t="n">
+      <c r="C49" s="2">
         <v>45352</v>
       </c>
-      <c r="D49" s="2" t="n">
+      <c r="D49" s="2">
         <v>46691</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="E49" s="3">
         <v>0.05</v>
       </c>
-      <c r="F49" s="1" t="n">
+      <c r="F49" s="1">
         <v>2</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H49" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I49" s="1" t="n">
+      <c r="H49" s="1">
+        <v>100</v>
+      </c>
+      <c r="I49" s="1">
         <v>100</v>
       </c>
       <c r="J49" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K49" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D50" s="2" t="n">
+      <c r="D50" s="2">
         <v>46691</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="E50" s="3">
         <v>0.05</v>
       </c>
-      <c r="F50" s="1" t="n">
+      <c r="F50" s="1">
         <v>2</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H50" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I50" s="1" t="n">
+      <c r="H50" s="1">
+        <v>100</v>
+      </c>
+      <c r="I50" s="1">
         <v>100</v>
       </c>
       <c r="J50" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K50" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D51" s="2" t="n">
+      <c r="D51" s="2">
         <v>46691</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="E51" s="3">
         <v>0.05</v>
       </c>
-      <c r="F51" s="1" t="n">
+      <c r="F51" s="1">
         <v>2</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H51" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I51" s="1" t="n">
+      <c r="H51" s="1">
+        <v>100</v>
+      </c>
+      <c r="I51" s="1">
         <v>100</v>
       </c>
       <c r="J51" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K51" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D52" s="2" t="n">
+      <c r="D52" s="2">
         <v>46691</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="E52" s="3">
         <v>0.05</v>
       </c>
-      <c r="F52" s="1" t="n">
+      <c r="F52" s="1">
         <v>2</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H52" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I52" s="1" t="n">
+      <c r="H52" s="1">
+        <v>100</v>
+      </c>
+      <c r="I52" s="1">
         <v>100</v>
       </c>
       <c r="J52" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K52" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D53" s="2" t="n">
+      <c r="D53" s="2">
         <v>46691</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="E53" s="3">
         <v>0.05</v>
       </c>
-      <c r="F53" s="1" t="n">
+      <c r="F53" s="1">
         <v>2</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H53" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I53" s="1" t="n">
+      <c r="H53" s="1">
+        <v>100</v>
+      </c>
+      <c r="I53" s="1">
         <v>100</v>
       </c>
       <c r="J53" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K53" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="2" t="n">
+      <c r="D54" s="2">
         <v>46691</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="E54" s="3">
         <v>0.05</v>
       </c>
-      <c r="F54" s="1" t="n">
+      <c r="F54" s="1">
         <v>2</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H54" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I54" s="1" t="n">
+      <c r="H54" s="1">
+        <v>100</v>
+      </c>
+      <c r="I54" s="1">
         <v>100</v>
       </c>
       <c r="J54" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K54" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D55" s="2" t="n">
+      <c r="D55" s="2">
         <v>46691</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="E55" s="3">
         <v>0.05</v>
       </c>
-      <c r="F55" s="1" t="n">
+      <c r="F55" s="1">
         <v>2</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H55" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I55" s="1" t="n">
+      <c r="H55" s="1">
+        <v>100</v>
+      </c>
+      <c r="I55" s="1">
         <v>100</v>
       </c>
       <c r="J55" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K55" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D56" s="2" t="n">
+      <c r="D56" s="2">
         <v>46691</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="E56" s="3">
         <v>0.05</v>
       </c>
-      <c r="F56" s="1" t="n">
+      <c r="F56" s="1">
         <v>2</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H56" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I56" s="1" t="n">
+      <c r="H56" s="1">
+        <v>100</v>
+      </c>
+      <c r="I56" s="1">
         <v>100</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K56" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D57" s="2" t="n">
+      <c r="D57" s="2">
         <v>46691</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="E57" s="3">
         <v>0.05</v>
       </c>
-      <c r="F57" s="1" t="n">
+      <c r="F57" s="1">
         <v>2</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H57" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I57" s="1" t="n">
+      <c r="H57" s="1">
+        <v>100</v>
+      </c>
+      <c r="I57" s="1">
         <v>100</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K57" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
         <v>74</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D58" s="2" t="n">
+      <c r="D58" s="2">
         <v>46173</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="E58" s="3">
         <v>0.03</v>
       </c>
-      <c r="F58" s="1" t="n">
+      <c r="F58" s="1">
         <v>4</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H58" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I58" s="1" t="n">
+      <c r="H58" s="1">
+        <v>100</v>
+      </c>
+      <c r="I58" s="1">
         <v>67</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K58" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D59" s="2" t="n">
+      <c r="D59" s="2">
         <v>46173</v>
       </c>
-      <c r="E59" s="3" t="n">
+      <c r="E59" s="3">
         <v>0.03</v>
       </c>
-      <c r="F59" s="1" t="n">
+      <c r="F59" s="1">
         <v>4</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H59" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I59" s="1" t="n">
+      <c r="H59" s="1">
+        <v>100</v>
+      </c>
+      <c r="I59" s="1">
         <v>67</v>
       </c>
       <c r="J59" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K59" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D60" s="2" t="n">
+      <c r="D60" s="2">
         <v>46173</v>
       </c>
-      <c r="E60" s="3" t="n">
+      <c r="E60" s="3">
         <v>0.03</v>
       </c>
-      <c r="F60" s="1" t="n">
+      <c r="F60" s="1">
         <v>4</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H60" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I60" s="1" t="n">
+      <c r="H60" s="1">
+        <v>100</v>
+      </c>
+      <c r="I60" s="1">
         <v>67</v>
       </c>
       <c r="J60" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K60" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D61" s="2" t="n">
+      <c r="D61" s="2">
         <v>46805</v>
       </c>
-      <c r="E61" s="3" t="n">
-        <v>0.3592</v>
-      </c>
-      <c r="F61" s="1" t="n">
+      <c r="E61" s="3">
+        <v>0.35920000000000002</v>
+      </c>
+      <c r="F61" s="1">
         <v>4</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H61" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I61" s="1" t="n">
+      <c r="H61" s="1">
+        <v>100</v>
+      </c>
+      <c r="I61" s="1">
         <v>100</v>
       </c>
       <c r="J61" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K61" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D62" s="2" t="n">
+      <c r="D62" s="2">
         <v>48397</v>
       </c>
-      <c r="E62" s="3" t="n">
-        <v>0.0663</v>
-      </c>
-      <c r="F62" s="1" t="n">
+      <c r="E62" s="3">
+        <v>6.6299999999999998E-2</v>
+      </c>
+      <c r="F62" s="1">
         <v>2</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H62" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I62" s="1" t="n">
+      <c r="H62" s="1">
+        <v>100</v>
+      </c>
+      <c r="I62" s="1">
         <v>100</v>
       </c>
       <c r="J62" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K62" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D63" s="2" t="n">
+      <c r="D63" s="2">
         <v>50284</v>
       </c>
-      <c r="E63" s="3" t="n">
-        <v>0.0588</v>
-      </c>
-      <c r="F63" s="1" t="n">
+      <c r="E63" s="3">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="F63" s="1">
         <v>2</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H63" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I63" s="1" t="n">
+      <c r="H63" s="1">
+        <v>100</v>
+      </c>
+      <c r="I63" s="1">
         <v>100</v>
       </c>
       <c r="J63" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K63" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>80</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D64" s="2" t="n">
+      <c r="D64" s="2">
         <v>50284</v>
       </c>
-      <c r="E64" s="3" t="n">
-        <v>0.0663</v>
-      </c>
-      <c r="F64" s="1" t="n">
+      <c r="E64" s="3">
+        <v>6.6299999999999998E-2</v>
+      </c>
+      <c r="F64" s="1">
         <v>2</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H64" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I64" s="1" t="n">
+      <c r="H64" s="1">
+        <v>100</v>
+      </c>
+      <c r="I64" s="1">
         <v>91.84</v>
       </c>
       <c r="J64" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K64" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D65" s="2" t="n">
+      <c r="D65" s="2">
         <v>50284</v>
       </c>
-      <c r="E65" s="3" t="n">
-        <v>0.0663</v>
-      </c>
-      <c r="F65" s="1" t="n">
+      <c r="E65" s="3">
+        <v>6.6299999999999998E-2</v>
+      </c>
+      <c r="F65" s="1">
         <v>2</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H65" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I65" s="1" t="n">
+      <c r="H65" s="1">
+        <v>100</v>
+      </c>
+      <c r="I65" s="1">
         <v>91.84</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K65" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D66" s="2" t="n">
+      <c r="D66" s="2">
         <v>50284</v>
       </c>
-      <c r="E66" s="3" t="n">
-        <v>0.0588</v>
-      </c>
-      <c r="F66" s="1" t="n">
+      <c r="E66" s="3">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="F66" s="1">
         <v>2</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H66" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I66" s="1" t="n">
+      <c r="H66" s="1">
+        <v>100</v>
+      </c>
+      <c r="I66" s="1">
         <v>100</v>
       </c>
       <c r="J66" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K66" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>83</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D67" s="2" t="n">
+      <c r="D67" s="2">
         <v>46084</v>
       </c>
-      <c r="E67" s="3" t="n">
+      <c r="E67" s="3">
         <v>0.08</v>
       </c>
-      <c r="F67" s="1" t="n">
+      <c r="F67" s="1">
         <v>2</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H67" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I67" s="1" t="n">
+      <c r="H67" s="1">
+        <v>100</v>
+      </c>
+      <c r="I67" s="1">
         <v>100</v>
       </c>
       <c r="J67" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K67" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>84</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D68" s="2" t="n">
+      <c r="D68" s="2">
         <v>46092</v>
       </c>
-      <c r="E68" s="3" t="n">
-        <v>0.0749</v>
-      </c>
-      <c r="F68" s="1" t="n">
+      <c r="E68" s="3">
+        <v>7.4899999999999994E-2</v>
+      </c>
+      <c r="F68" s="1">
         <v>2</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H68" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I68" s="1" t="n">
+      <c r="H68" s="1">
+        <v>100</v>
+      </c>
+      <c r="I68" s="1">
         <v>100</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>11</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
         <v>85</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D69" s="2" t="n">
+      <c r="D69" s="2">
         <v>46170</v>
       </c>
-      <c r="E69" s="3" t="n">
+      <c r="E69" s="3">
         <v>0.06</v>
       </c>
-      <c r="F69" s="1" t="n">
+      <c r="F69" s="1">
         <v>4</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H69" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I69" s="1" t="n">
+      <c r="H69" s="1">
+        <v>100</v>
+      </c>
+      <c r="I69" s="1">
         <v>100</v>
       </c>
       <c r="J69" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="70" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K69" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>86</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D70" s="2" t="n">
+      <c r="C70" s="1"/>
+      <c r="D70" s="2">
         <v>46186</v>
       </c>
-      <c r="E70" s="3" t="n">
+      <c r="E70" s="3">
         <v>0.06</v>
       </c>
-      <c r="F70" s="1" t="n">
+      <c r="F70" s="1">
         <v>4</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H70" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I70" s="1" t="n">
+      <c r="H70" s="1">
+        <v>100</v>
+      </c>
+      <c r="I70" s="1">
         <v>100</v>
       </c>
       <c r="J70" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="71" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K70" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
         <v>87</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D71" s="2" t="n">
+      <c r="C71" s="1"/>
+      <c r="D71" s="2">
         <v>46348</v>
       </c>
-      <c r="E71" s="3" t="n">
-        <v>0.0975</v>
-      </c>
-      <c r="F71" s="1" t="n">
+      <c r="E71" s="3">
+        <v>9.7500000000000003E-2</v>
+      </c>
+      <c r="F71" s="1">
         <v>2</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H71" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I71" s="1" t="n">
+      <c r="H71" s="1">
+        <v>100</v>
+      </c>
+      <c r="I71" s="1">
         <v>100</v>
       </c>
       <c r="J71" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="72" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K71" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>88</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D72" s="2" t="n">
+      <c r="C72" s="1"/>
+      <c r="D72" s="2">
         <v>46683</v>
       </c>
-      <c r="E72" s="3" t="n">
-        <v>0.0575</v>
-      </c>
-      <c r="F72" s="1" t="n">
+      <c r="E72" s="3">
+        <v>5.7500000000000002E-2</v>
+      </c>
+      <c r="F72" s="1">
         <v>2</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H72" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I72" s="1" t="n">
+      <c r="H72" s="1">
+        <v>100</v>
+      </c>
+      <c r="I72" s="1">
         <v>100</v>
       </c>
       <c r="J72" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="73" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K72" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
         <v>89</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D73" s="2" t="n">
+      <c r="C73" s="1"/>
+      <c r="D73" s="2">
         <v>47070</v>
       </c>
-      <c r="E73" s="3" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="F73" s="1" t="n">
+      <c r="E73" s="3">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F73" s="1">
         <v>2</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H73" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I73" s="1" t="n">
+      <c r="H73" s="1">
+        <v>100</v>
+      </c>
+      <c r="I73" s="1">
         <v>100</v>
       </c>
       <c r="J73" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="74" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K73" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
         <v>90</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D74" s="2" t="n">
+      <c r="C74" s="1"/>
+      <c r="D74" s="2">
         <v>47388</v>
       </c>
-      <c r="E74" s="3" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="F74" s="1" t="n">
+      <c r="E74" s="3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F74" s="1">
         <v>2</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H74" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I74" s="1" t="n">
+      <c r="H74" s="1">
+        <v>100</v>
+      </c>
+      <c r="I74" s="1">
         <v>100</v>
       </c>
       <c r="J74" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="75" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K74" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
         <v>91</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D75" s="2" t="n">
+      <c r="C75" s="1"/>
+      <c r="D75" s="2">
         <v>47414</v>
       </c>
-      <c r="E75" s="3" t="n">
-        <v>0.0725</v>
-      </c>
-      <c r="F75" s="1" t="n">
+      <c r="E75" s="3">
+        <v>7.2499999999999995E-2</v>
+      </c>
+      <c r="F75" s="1">
         <v>2</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H75" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I75" s="1" t="n">
+      <c r="H75" s="1">
+        <v>100</v>
+      </c>
+      <c r="I75" s="1">
         <v>100</v>
       </c>
       <c r="J75" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K75" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D76" s="2" t="n">
+      <c r="D76" s="2">
         <v>47357</v>
       </c>
-      <c r="E76" s="3" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="F76" s="1" t="n">
+      <c r="E76" s="3">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="F76" s="1">
         <v>2</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H76" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I76" s="1" t="n">
+      <c r="H76" s="1">
+        <v>100</v>
+      </c>
+      <c r="I76" s="1">
         <v>100</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>11</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
         <v>93</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D77" s="2" t="n">
+      <c r="D77" s="2">
         <v>48131</v>
       </c>
-      <c r="E77" s="3" t="n">
-        <v>0.0765</v>
-      </c>
-      <c r="F77" s="1" t="n">
+      <c r="E77" s="3">
+        <v>7.6499999999999999E-2</v>
+      </c>
+      <c r="F77" s="1">
         <v>2</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H77" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I77" s="1" t="n">
+      <c r="H77" s="1">
+        <v>100</v>
+      </c>
+      <c r="I77" s="1">
         <v>100</v>
       </c>
       <c r="J77" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="78" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K77" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
         <v>94</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D78" s="2" t="n">
+      <c r="C78" s="1"/>
+      <c r="D78" s="2">
         <v>48165</v>
       </c>
-      <c r="E78" s="3" t="n">
-        <v>0.0725</v>
-      </c>
-      <c r="F78" s="1" t="n">
+      <c r="E78" s="3">
+        <v>7.2499999999999995E-2</v>
+      </c>
+      <c r="F78" s="1">
         <v>2</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H78" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I78" s="1" t="n">
+      <c r="H78" s="1">
+        <v>100</v>
+      </c>
+      <c r="I78" s="1">
         <v>100</v>
       </c>
       <c r="J78" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="79" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K78" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>95</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D79" s="2" t="n">
+      <c r="C79" s="1"/>
+      <c r="D79" s="2">
         <v>48727</v>
       </c>
-      <c r="E79" s="3" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="F79" s="1" t="n">
+      <c r="E79" s="3">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="F79" s="1">
         <v>2</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H79" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I79" s="1" t="n">
+      <c r="H79" s="1">
+        <v>100</v>
+      </c>
+      <c r="I79" s="1">
         <v>100</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="80" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>11</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
         <v>96</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D80" s="2" t="n">
+      <c r="C80" s="1"/>
+      <c r="D80" s="2">
         <v>46203</v>
       </c>
-      <c r="E80" s="3" t="n">
+      <c r="E80" s="3">
         <v>0.1095</v>
       </c>
-      <c r="F80" s="1" t="n">
+      <c r="F80" s="1">
         <v>4</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H80" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I80" s="1" t="n">
+      <c r="H80" s="1">
+        <v>100</v>
+      </c>
+      <c r="I80" s="1">
         <v>100</v>
       </c>
       <c r="J80" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="81" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K80" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
         <v>97</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D81" s="2" t="n">
+      <c r="C81" s="1"/>
+      <c r="D81" s="2">
         <v>46221</v>
       </c>
-      <c r="E81" s="3" t="n">
+      <c r="E81" s="3">
         <v>0.08</v>
       </c>
-      <c r="F81" s="1" t="n">
+      <c r="F81" s="1">
         <v>2</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H81" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I81" s="1" t="n">
+      <c r="H81" s="1">
+        <v>100</v>
+      </c>
+      <c r="I81" s="1">
         <v>100</v>
       </c>
       <c r="J81" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="82" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K81" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>98</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D82" s="2" t="n">
+      <c r="C82" s="1"/>
+      <c r="D82" s="2">
         <v>46507</v>
       </c>
-      <c r="E82" s="3" t="n">
-        <v>0.0913</v>
-      </c>
-      <c r="F82" s="1" t="n">
+      <c r="E82" s="3">
+        <v>9.1300000000000006E-2</v>
+      </c>
+      <c r="F82" s="1">
         <v>2</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H82" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I82" s="1" t="n">
+      <c r="H82" s="1">
+        <v>100</v>
+      </c>
+      <c r="I82" s="1">
         <v>100</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="83" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>11</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>99</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D83" s="2" t="n">
+      <c r="C83" s="1"/>
+      <c r="D83" s="2">
         <v>47292</v>
       </c>
-      <c r="E83" s="3" t="n">
+      <c r="E83" s="3">
         <v>0.08</v>
       </c>
-      <c r="F83" s="1" t="n">
+      <c r="F83" s="1">
         <v>2</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H83" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I83" s="1" t="n">
+      <c r="H83" s="1">
+        <v>100</v>
+      </c>
+      <c r="I83" s="1">
         <v>100</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="84" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>11</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
         <v>100</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D84" s="2" t="n">
+      <c r="C84" s="1"/>
+      <c r="D84" s="2">
         <v>47299</v>
       </c>
-      <c r="E84" s="3" t="n">
+      <c r="E84" s="3">
         <v>0.09</v>
       </c>
-      <c r="F84" s="1" t="n">
+      <c r="F84" s="1">
         <v>2</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H84" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I84" s="1" t="n">
+      <c r="H84" s="1">
+        <v>100</v>
+      </c>
+      <c r="I84" s="1">
         <v>100</v>
       </c>
       <c r="J84" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="85" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K84" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>101</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D85" s="2" t="n">
+      <c r="C85" s="1"/>
+      <c r="D85" s="2">
         <v>47686</v>
       </c>
-      <c r="E85" s="3" t="n">
-        <v>0.0875</v>
-      </c>
-      <c r="F85" s="1" t="n">
+      <c r="E85" s="3">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="F85" s="1">
         <v>2</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H85" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I85" s="1" t="n">
+      <c r="H85" s="1">
+        <v>100</v>
+      </c>
+      <c r="I85" s="1">
         <v>100</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>11</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
         <v>102</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D86" s="2" t="n">
+      <c r="D86" s="2">
         <v>48047</v>
       </c>
-      <c r="E86" s="3" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="F86" s="1" t="n">
+      <c r="E86" s="3">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="F86" s="1">
         <v>2</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H86" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I86" s="1" t="n">
+      <c r="H86" s="1">
+        <v>100</v>
+      </c>
+      <c r="I86" s="1">
         <v>100</v>
       </c>
       <c r="J86" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="87" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K86" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D87" s="2" t="n">
+      <c r="C87" s="1"/>
+      <c r="D87" s="2">
         <v>48102</v>
       </c>
-      <c r="E87" s="3" t="n">
-        <v>0.0875</v>
-      </c>
-      <c r="F87" s="1" t="n">
+      <c r="E87" s="3">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="F87" s="1">
         <v>2</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H87" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I87" s="1" t="n">
+      <c r="H87" s="1">
+        <v>100</v>
+      </c>
+      <c r="I87" s="1">
         <v>100</v>
       </c>
       <c r="J87" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K87" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>104</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D88" s="2" t="n">
+      <c r="D88" s="2">
         <v>48364</v>
       </c>
-      <c r="E88" s="3" t="n">
-        <v>0.085</v>
-      </c>
-      <c r="F88" s="1" t="n">
+      <c r="E88" s="3">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="F88" s="1">
         <v>2</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H88" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I88" s="1" t="n">
+      <c r="H88" s="1">
+        <v>100</v>
+      </c>
+      <c r="I88" s="1">
         <v>100</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>11</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
         <v>105</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D89" s="2" t="n">
+      <c r="D89" s="2">
         <v>48503</v>
       </c>
-      <c r="E89" s="3" t="n">
-        <v>0.0788</v>
-      </c>
-      <c r="F89" s="1" t="n">
+      <c r="E89" s="3">
+        <v>7.8799999999999995E-2</v>
+      </c>
+      <c r="F89" s="1">
         <v>2</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H89" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I89" s="1" t="n">
+      <c r="H89" s="1">
+        <v>100</v>
+      </c>
+      <c r="I89" s="1">
         <v>100</v>
       </c>
       <c r="J89" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K89" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>106</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D90" s="2" t="n">
+      <c r="D90" s="2">
         <v>48740</v>
       </c>
-      <c r="E90" s="3" t="n">
-        <v>0.085</v>
-      </c>
-      <c r="F90" s="1" t="n">
+      <c r="E90" s="3">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="F90" s="1">
         <v>2</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H90" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I90" s="1" t="n">
+      <c r="H90" s="1">
+        <v>100</v>
+      </c>
+      <c r="I90" s="1">
         <v>100</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>11</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
         <v>107</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D91" s="2" t="n">
+      <c r="D91" s="2">
         <v>48852</v>
       </c>
-      <c r="E91" s="3" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="F91" s="1" t="n">
+      <c r="E91" s="3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F91" s="1">
         <v>2</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H91" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I91" s="1" t="n">
+      <c r="H91" s="1">
+        <v>100</v>
+      </c>
+      <c r="I91" s="1">
         <v>100</v>
       </c>
       <c r="J91" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="92" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K91" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>108</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D92" s="2" t="n">
+      <c r="C92" s="1"/>
+      <c r="D92" s="2">
         <v>49399</v>
       </c>
-      <c r="E92" s="3" t="n">
+      <c r="E92" s="3">
         <v>0.08</v>
       </c>
-      <c r="F92" s="1" t="n">
+      <c r="F92" s="1">
         <v>2</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H92" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I92" s="1" t="n">
+      <c r="H92" s="1">
+        <v>100</v>
+      </c>
+      <c r="I92" s="1">
         <v>100</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="93" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>11</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
         <v>109</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D93" s="2" t="n">
+      <c r="C93" s="1"/>
+      <c r="D93" s="2">
         <v>49653</v>
       </c>
-      <c r="E93" s="3" t="n">
-        <v>0.0763</v>
-      </c>
-      <c r="F93" s="1" t="n">
+      <c r="E93" s="3">
+        <v>7.6300000000000007E-2</v>
+      </c>
+      <c r="F93" s="1">
         <v>2</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H93" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I93" s="1" t="n">
+      <c r="H93" s="1">
+        <v>100</v>
+      </c>
+      <c r="I93" s="1">
         <v>100</v>
       </c>
       <c r="J93" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="94" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K93" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
         <v>110</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D94" s="2" t="n">
+      <c r="C94" s="1"/>
+      <c r="D94" s="2">
         <v>48961</v>
       </c>
-      <c r="E94" s="3" t="n">
-        <v>0.0875</v>
-      </c>
-      <c r="F94" s="1" t="n">
+      <c r="E94" s="3">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="F94" s="1">
         <v>2</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H94" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I94" s="1" t="n">
+      <c r="H94" s="1">
+        <v>100</v>
+      </c>
+      <c r="I94" s="1">
         <v>100</v>
       </c>
       <c r="J94" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K94" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C95" s="1"/>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C96" s="1"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C97" s="1"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C98" s="1"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="99" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C99" s="1"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C100" s="1"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C101" s="1"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C102" s="1"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C103" s="1"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C104" s="1"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C105" s="1"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C106" s="1"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C107" s="1"/>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C108" s="1"/>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C109" s="1"/>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C110" s="1"/>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C111" s="1"/>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C112" s="1"/>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C113" s="1"/>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C114" s="1"/>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C115" s="1"/>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C116" s="1"/>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C117" s="1"/>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C118" s="1"/>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C119" s="1"/>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C120" s="1"/>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C121" s="1"/>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C122" s="1"/>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C123" s="1"/>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C124" s="1"/>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C125" s="1"/>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C126" s="1"/>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C127" s="1"/>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C128" s="1"/>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C129" s="1"/>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C130" s="1"/>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C131" s="1"/>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C132" s="1"/>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C133" s="1"/>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C134" s="1"/>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C135" s="1"/>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C136" s="1"/>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C137" s="1"/>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C138" s="1"/>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C139" s="1"/>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C140" s="1"/>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C141" s="1"/>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C142" s="1"/>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C143" s="1"/>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C144" s="1"/>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C145" s="1"/>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C146" s="1"/>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C147" s="1"/>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C148" s="1"/>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C149" s="1"/>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C150" s="1"/>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C151" s="1"/>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C152" s="1"/>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C153" s="1"/>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C154" s="1"/>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C155" s="1"/>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C156" s="1"/>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C157" s="1"/>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C158" s="1"/>
     </row>
-    <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1048576" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultColWidth="8.21875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>119</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/data/SPR_BS_master.xlsx
+++ b/data/SPR_BS_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\SPR-BS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E862E4-E0E7-4FC5-9BA4-5091DFF1445C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97786A01-22A6-45F5-9333-844A13F3DCE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -439,7 +439,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -450,6 +450,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -480,7 +492,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -501,6 +513,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2267,7 +2288,7 @@
       </c>
     </row>
     <row r="46" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="8" t="s">
         <v>60</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -2302,7 +2323,7 @@
       </c>
     </row>
     <row r="47" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="10" t="s">
         <v>61</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -2337,7 +2358,7 @@
       </c>
     </row>
     <row r="48" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="10" t="s">
         <v>62</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -2369,7 +2390,7 @@
       </c>
     </row>
     <row r="49" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="10" t="s">
         <v>63</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -2532,7 +2553,7 @@
       </c>
     </row>
     <row r="54" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="9" t="s">
         <v>69</v>
       </c>
       <c r="B54" s="1" t="s">
@@ -2564,7 +2585,7 @@
       </c>
     </row>
     <row r="55" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="9" t="s">
         <v>71</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -2596,7 +2617,7 @@
       </c>
     </row>
     <row r="56" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="9" t="s">
         <v>72</v>
       </c>
       <c r="B56" s="1" t="s">
@@ -2628,7 +2649,7 @@
       </c>
     </row>
     <row r="57" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="9" t="s">
         <v>73</v>
       </c>
       <c r="B57" s="1" t="s">

--- a/data/SPR_BS_master.xlsx
+++ b/data/SPR_BS_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\SPR-BS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97786A01-22A6-45F5-9333-844A13F3DCE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88742377-E2DD-4382-96A4-A188F83AEBB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="master_bono" sheetId="1" r:id="rId1"/>
@@ -1817,7 +1817,7 @@
         <v>44</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="C32" s="2">
         <v>44078</v>
@@ -2323,7 +2323,7 @@
       </c>
     </row>
     <row r="47" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -2358,7 +2358,7 @@
       </c>
     </row>
     <row r="48" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -2390,7 +2390,7 @@
       </c>
     </row>
     <row r="49" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -2557,7 +2557,7 @@
         <v>69</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D54" s="2">
         <v>46691</v>
@@ -2589,7 +2589,7 @@
         <v>71</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D55" s="2">
         <v>46691</v>
@@ -2621,7 +2621,7 @@
         <v>72</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D56" s="2">
         <v>46691</v>
@@ -2653,7 +2653,7 @@
         <v>73</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D57" s="2">
         <v>46691</v>
@@ -2681,7 +2681,7 @@
       </c>
     </row>
     <row r="58" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="10" t="s">
         <v>74</v>
       </c>
       <c r="B58" s="1" t="s">
@@ -2713,11 +2713,11 @@
       </c>
     </row>
     <row r="59" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="9" t="s">
         <v>75</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D59" s="2">
         <v>46173</v>
@@ -2873,7 +2873,7 @@
       </c>
     </row>
     <row r="64" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="10" t="s">
         <v>80</v>
       </c>
       <c r="B64" s="7" t="s">
@@ -2905,7 +2905,7 @@
       </c>
     </row>
     <row r="65" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="9" t="s">
         <v>81</v>
       </c>
       <c r="B65" s="1" t="s">

--- a/data/SPR_BS_master.xlsx
+++ b/data/SPR_BS_master.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\SPR-BS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88742377-E2DD-4382-96A4-A188F83AEBB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E71999E-D957-4068-AD67-3AC30AF397CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="master_bono" sheetId="1" r:id="rId1"/>
     <sheet name="README" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -492,7 +492,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -519,9 +519,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2681,7 +2678,7 @@
       </c>
     </row>
     <row r="58" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A58" s="10" t="s">
+      <c r="A58" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B58" s="1" t="s">
@@ -2873,7 +2870,7 @@
       </c>
     </row>
     <row r="64" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A64" s="10" t="s">
+      <c r="A64" s="1" t="s">
         <v>80</v>
       </c>
       <c r="B64" s="7" t="s">

--- a/data/SPR_BS_master.xlsx
+++ b/data/SPR_BS_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\SPR-BS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E71999E-D957-4068-AD67-3AC30AF397CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9928067-7160-4DEE-89B9-8B8787C7083D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="140">
   <si>
     <t>codigo</t>
   </si>
@@ -406,6 +406,57 @@
   </si>
   <si>
     <t>SOBERANO</t>
+  </si>
+  <si>
+    <t>S27F6</t>
+  </si>
+  <si>
+    <t>LECAP</t>
+  </si>
+  <si>
+    <t>S17A6</t>
+  </si>
+  <si>
+    <t>S16M6</t>
+  </si>
+  <si>
+    <t>S30A6</t>
+  </si>
+  <si>
+    <t>S29Y6</t>
+  </si>
+  <si>
+    <t>S31L6</t>
+  </si>
+  <si>
+    <t>S31G6</t>
+  </si>
+  <si>
+    <t>S30O6</t>
+  </si>
+  <si>
+    <t>S30N6</t>
+  </si>
+  <si>
+    <t>T13F6</t>
+  </si>
+  <si>
+    <t>BONCAP</t>
+  </si>
+  <si>
+    <t>T30J6</t>
+  </si>
+  <si>
+    <t>T15E7</t>
+  </si>
+  <si>
+    <t>T30A7</t>
+  </si>
+  <si>
+    <t>T31Y7</t>
+  </si>
+  <si>
+    <t>T30J7</t>
   </si>
 </sst>
 </file>
@@ -717,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1048576"/>
+  <dimension ref="A1:K158"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="15.33203125" style="1" customWidth="1"/>
@@ -2285,26 +2336,24 @@
       </c>
     </row>
     <row r="46" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="8" t="s">
-        <v>60</v>
+      <c r="A46" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C46" s="2">
-        <v>45296</v>
-      </c>
+      <c r="C46" s="1"/>
       <c r="D46" s="2">
-        <v>46691</v>
+        <v>46080</v>
       </c>
       <c r="E46" s="3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F46" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H46" s="1">
         <v>100</v>
@@ -2316,30 +2365,28 @@
         <v>11</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C47" s="2">
-        <v>45596</v>
-      </c>
+      <c r="C47" s="1"/>
       <c r="D47" s="2">
-        <v>46691</v>
+        <v>46129</v>
       </c>
       <c r="E47" s="3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F47" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H47" s="1">
         <v>100</v>
@@ -2351,27 +2398,28 @@
         <v>11</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>62</v>
+        <v>126</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="C48" s="1"/>
       <c r="D48" s="2">
-        <v>46691</v>
+        <v>46097</v>
       </c>
       <c r="E48" s="3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F48" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H48" s="1">
         <v>100</v>
@@ -2383,30 +2431,28 @@
         <v>11</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C49" s="2">
-        <v>45352</v>
-      </c>
+      <c r="C49" s="1"/>
       <c r="D49" s="2">
-        <v>46691</v>
+        <v>46142</v>
       </c>
       <c r="E49" s="3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F49" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H49" s="1">
         <v>100</v>
@@ -2418,27 +2464,28 @@
         <v>11</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>65</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C50" s="1"/>
       <c r="D50" s="2">
-        <v>46691</v>
+        <v>46171</v>
       </c>
       <c r="E50" s="3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F50" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H50" s="1">
         <v>100</v>
@@ -2447,30 +2494,31 @@
         <v>100</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>66</v>
+        <v>129</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>65</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C51" s="1"/>
       <c r="D51" s="2">
-        <v>46691</v>
+        <v>46234</v>
       </c>
       <c r="E51" s="3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F51" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H51" s="1">
         <v>100</v>
@@ -2479,30 +2527,31 @@
         <v>100</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>65</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C52" s="1"/>
       <c r="D52" s="2">
-        <v>46691</v>
+        <v>46265</v>
       </c>
       <c r="E52" s="3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F52" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H52" s="1">
         <v>100</v>
@@ -2511,30 +2560,31 @@
         <v>100</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>68</v>
+        <v>131</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>65</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C53" s="1"/>
       <c r="D53" s="2">
-        <v>46691</v>
+        <v>46325</v>
       </c>
       <c r="E53" s="3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F53" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H53" s="1">
         <v>100</v>
@@ -2543,30 +2593,31 @@
         <v>100</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A54" s="9" t="s">
-        <v>69</v>
+      <c r="A54" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>18</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C54" s="1"/>
       <c r="D54" s="2">
-        <v>46691</v>
+        <v>46356</v>
       </c>
       <c r="E54" s="3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F54" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H54" s="1">
         <v>100</v>
@@ -2575,30 +2626,31 @@
         <v>100</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A55" s="9" t="s">
-        <v>71</v>
+      <c r="A55" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>18</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C55" s="1"/>
       <c r="D55" s="2">
-        <v>46691</v>
+        <v>46066</v>
       </c>
       <c r="E55" s="3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F55" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H55" s="1">
         <v>100</v>
@@ -2607,30 +2659,31 @@
         <v>100</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A56" s="9" t="s">
-        <v>72</v>
+      <c r="A56" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>18</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C56" s="1"/>
       <c r="D56" s="2">
-        <v>46691</v>
+        <v>46203</v>
       </c>
       <c r="E56" s="3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F56" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H56" s="1">
         <v>100</v>
@@ -2639,30 +2692,31 @@
         <v>100</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A57" s="9" t="s">
-        <v>73</v>
+      <c r="A57" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>18</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C57" s="1"/>
       <c r="D57" s="2">
-        <v>46691</v>
+        <v>46402</v>
       </c>
       <c r="E57" s="3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F57" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H57" s="1">
         <v>100</v>
@@ -2671,126 +2725,132 @@
         <v>100</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="C58" s="1"/>
       <c r="D58" s="2">
-        <v>46173</v>
+        <v>46507</v>
       </c>
       <c r="E58" s="3">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F58" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H58" s="1">
         <v>100</v>
       </c>
       <c r="I58" s="1">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A59" s="9" t="s">
-        <v>75</v>
+      <c r="A59" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>18</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C59" s="1"/>
       <c r="D59" s="2">
-        <v>46173</v>
+        <v>46538</v>
       </c>
       <c r="E59" s="3">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F59" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H59" s="1">
         <v>100</v>
       </c>
       <c r="I59" s="1">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>76</v>
+        <v>139</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>65</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C60" s="1"/>
       <c r="D60" s="2">
-        <v>46173</v>
+        <v>46568</v>
       </c>
       <c r="E60" s="3">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F60" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H60" s="1">
         <v>100</v>
       </c>
       <c r="I60" s="1">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A61" s="1" t="s">
-        <v>77</v>
+      <c r="A61" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="C61" s="2">
+        <v>45296</v>
+      </c>
       <c r="D61" s="2">
-        <v>46805</v>
+        <v>46691</v>
       </c>
       <c r="E61" s="3">
-        <v>0.35920000000000002</v>
+        <v>0.05</v>
       </c>
       <c r="F61" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H61" s="1">
         <v>100</v>
@@ -2807,16 +2867,19 @@
     </row>
     <row r="62" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
+      </c>
+      <c r="C62" s="2">
+        <v>45596</v>
       </c>
       <c r="D62" s="2">
-        <v>48397</v>
+        <v>46691</v>
       </c>
       <c r="E62" s="3">
-        <v>6.6299999999999998E-2</v>
+        <v>0.05</v>
       </c>
       <c r="F62" s="1">
         <v>2</v>
@@ -2831,7 +2894,7 @@
         <v>100</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K62" s="1" t="s">
         <v>122</v>
@@ -2839,16 +2902,16 @@
     </row>
     <row r="63" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D63" s="2">
-        <v>50284</v>
+        <v>46691</v>
       </c>
       <c r="E63" s="3">
-        <v>5.8799999999999998E-2</v>
+        <v>0.05</v>
       </c>
       <c r="F63" s="1">
         <v>2</v>
@@ -2871,16 +2934,19 @@
     </row>
     <row r="64" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>18</v>
+        <v>63</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="2">
+        <v>45352</v>
       </c>
       <c r="D64" s="2">
-        <v>50284</v>
+        <v>46691</v>
       </c>
       <c r="E64" s="3">
-        <v>6.6299999999999998E-2</v>
+        <v>0.05</v>
       </c>
       <c r="F64" s="1">
         <v>2</v>
@@ -2892,7 +2958,7 @@
         <v>100</v>
       </c>
       <c r="I64" s="1">
-        <v>91.84</v>
+        <v>100</v>
       </c>
       <c r="J64" s="1" t="s">
         <v>11</v>
@@ -2902,17 +2968,17 @@
       </c>
     </row>
     <row r="65" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A65" s="9" t="s">
-        <v>81</v>
+      <c r="A65" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="D65" s="2">
-        <v>50284</v>
+        <v>46691</v>
       </c>
       <c r="E65" s="3">
-        <v>6.6299999999999998E-2</v>
+        <v>0.05</v>
       </c>
       <c r="F65" s="1">
         <v>2</v>
@@ -2924,10 +2990,10 @@
         <v>100</v>
       </c>
       <c r="I65" s="1">
-        <v>91.84</v>
+        <v>100</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="K65" s="1" t="s">
         <v>122</v>
@@ -2935,16 +3001,16 @@
     </row>
     <row r="66" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="D66" s="2">
-        <v>50284</v>
+        <v>46691</v>
       </c>
       <c r="E66" s="3">
-        <v>5.8799999999999998E-2</v>
+        <v>0.05</v>
       </c>
       <c r="F66" s="1">
         <v>2</v>
@@ -2959,30 +3025,30 @@
         <v>100</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="K66" s="1" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A67" s="6" t="s">
-        <v>83</v>
+      <c r="A67" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="D67" s="2">
-        <v>46084</v>
+        <v>46691</v>
       </c>
       <c r="E67" s="3">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="F67" s="1">
         <v>2</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H67" s="1">
         <v>100</v>
@@ -2991,30 +3057,30 @@
         <v>100</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="D68" s="2">
-        <v>46092</v>
+        <v>46691</v>
       </c>
       <c r="E68" s="3">
-        <v>7.4899999999999994E-2</v>
+        <v>0.05</v>
       </c>
       <c r="F68" s="1">
         <v>2</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H68" s="1">
         <v>100</v>
@@ -3023,257 +3089,251 @@
         <v>100</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A69" s="6" t="s">
-        <v>85</v>
+      <c r="A69" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D69" s="2">
-        <v>46170</v>
+        <v>46691</v>
       </c>
       <c r="E69" s="3">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F69" s="1">
+        <v>2</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H69" s="1">
+        <v>100</v>
+      </c>
+      <c r="I69" s="1">
+        <v>100</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A70" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D70" s="2">
+        <v>46691</v>
+      </c>
+      <c r="E70" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="F70" s="1">
+        <v>2</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H70" s="1">
+        <v>100</v>
+      </c>
+      <c r="I70" s="1">
+        <v>100</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A71" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D71" s="2">
+        <v>46691</v>
+      </c>
+      <c r="E71" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="F71" s="1">
+        <v>2</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H71" s="1">
+        <v>100</v>
+      </c>
+      <c r="I71" s="1">
+        <v>100</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A72" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D72" s="2">
+        <v>46691</v>
+      </c>
+      <c r="E72" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="F72" s="1">
+        <v>2</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H72" s="1">
+        <v>100</v>
+      </c>
+      <c r="I72" s="1">
+        <v>100</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D73" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E73" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="F73" s="1">
         <v>4</v>
       </c>
-      <c r="G69" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H69" s="1">
-        <v>100</v>
-      </c>
-      <c r="I69" s="1">
-        <v>100</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A70" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C70" s="1"/>
-      <c r="D70" s="2">
-        <v>46186</v>
-      </c>
-      <c r="E70" s="3">
-        <v>0.06</v>
-      </c>
-      <c r="F70" s="1">
+      <c r="G73" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H73" s="1">
+        <v>100</v>
+      </c>
+      <c r="I73" s="1">
+        <v>67</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A74" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D74" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E74" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="F74" s="1">
         <v>4</v>
       </c>
-      <c r="G70" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H70" s="1">
-        <v>100</v>
-      </c>
-      <c r="I70" s="1">
-        <v>100</v>
-      </c>
-      <c r="J70" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A71" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C71" s="1"/>
-      <c r="D71" s="2">
-        <v>46348</v>
-      </c>
-      <c r="E71" s="3">
-        <v>9.7500000000000003E-2</v>
-      </c>
-      <c r="F71" s="1">
-        <v>2</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H71" s="1">
-        <v>100</v>
-      </c>
-      <c r="I71" s="1">
-        <v>100</v>
-      </c>
-      <c r="J71" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A72" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C72" s="1"/>
-      <c r="D72" s="2">
-        <v>46683</v>
-      </c>
-      <c r="E72" s="3">
-        <v>5.7500000000000002E-2</v>
-      </c>
-      <c r="F72" s="1">
-        <v>2</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H72" s="1">
-        <v>100</v>
-      </c>
-      <c r="I72" s="1">
-        <v>100</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A73" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C73" s="1"/>
-      <c r="D73" s="2">
-        <v>47070</v>
-      </c>
-      <c r="E73" s="3">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F73" s="1">
-        <v>2</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H73" s="1">
-        <v>100</v>
-      </c>
-      <c r="I73" s="1">
-        <v>100</v>
-      </c>
-      <c r="J73" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A74" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C74" s="1"/>
-      <c r="D74" s="2">
-        <v>47388</v>
-      </c>
-      <c r="E74" s="3">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="F74" s="1">
-        <v>2</v>
-      </c>
       <c r="G74" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H74" s="1">
         <v>100</v>
       </c>
       <c r="I74" s="1">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A75" s="6" t="s">
-        <v>91</v>
+      <c r="A75" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C75" s="1"/>
+        <v>65</v>
+      </c>
       <c r="D75" s="2">
-        <v>47414</v>
+        <v>46173</v>
       </c>
       <c r="E75" s="3">
-        <v>7.2499999999999995E-2</v>
+        <v>0.03</v>
       </c>
       <c r="F75" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H75" s="1">
         <v>100</v>
       </c>
       <c r="I75" s="1">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D76" s="2">
-        <v>47357</v>
+        <v>46805</v>
       </c>
       <c r="E76" s="3">
-        <v>7.4999999999999997E-2</v>
+        <v>0.35920000000000002</v>
       </c>
       <c r="F76" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>20</v>
@@ -3288,27 +3348,27 @@
         <v>11</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A77" s="6" t="s">
-        <v>93</v>
+      <c r="A77" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D77" s="2">
-        <v>48131</v>
+        <v>48397</v>
       </c>
       <c r="E77" s="3">
-        <v>7.6499999999999999E-2</v>
+        <v>6.6299999999999998E-2</v>
       </c>
       <c r="F77" s="1">
         <v>2</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H77" s="1">
         <v>100</v>
@@ -3317,31 +3377,30 @@
         <v>100</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A78" s="6" t="s">
-        <v>94</v>
+      <c r="A78" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C78" s="1"/>
+        <v>11</v>
+      </c>
       <c r="D78" s="2">
-        <v>48165</v>
+        <v>50284</v>
       </c>
       <c r="E78" s="3">
-        <v>7.2499999999999995E-2</v>
+        <v>5.8799999999999998E-2</v>
       </c>
       <c r="F78" s="1">
         <v>2</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H78" s="1">
         <v>100</v>
@@ -3353,22 +3412,21 @@
         <v>11</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C79" s="1"/>
+        <v>80</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="D79" s="2">
-        <v>48727</v>
+        <v>50284</v>
       </c>
       <c r="E79" s="3">
-        <v>9.5000000000000001E-2</v>
+        <v>6.6299999999999998E-2</v>
       </c>
       <c r="F79" s="1">
         <v>2</v>
@@ -3380,100 +3438,97 @@
         <v>100</v>
       </c>
       <c r="I79" s="1">
-        <v>100</v>
+        <v>91.84</v>
       </c>
       <c r="J79" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A80" s="6" t="s">
-        <v>96</v>
+      <c r="A80" s="9" t="s">
+        <v>81</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C80" s="1"/>
       <c r="D80" s="2">
-        <v>46203</v>
+        <v>50284</v>
       </c>
       <c r="E80" s="3">
-        <v>0.1095</v>
+        <v>6.6299999999999998E-2</v>
       </c>
       <c r="F80" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H80" s="1">
         <v>100</v>
       </c>
       <c r="I80" s="1">
-        <v>100</v>
+        <v>91.84</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A81" s="6" t="s">
-        <v>97</v>
+      <c r="A81" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C81" s="1"/>
       <c r="D81" s="2">
-        <v>46221</v>
+        <v>50284</v>
       </c>
       <c r="E81" s="3">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="F81" s="1">
+        <v>2</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H81" s="1">
+        <v>100</v>
+      </c>
+      <c r="I81" s="1">
+        <v>100</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A82" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D82" s="2">
+        <v>46084</v>
+      </c>
+      <c r="E82" s="3">
         <v>0.08</v>
       </c>
-      <c r="F81" s="1">
-        <v>2</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H81" s="1">
-        <v>100</v>
-      </c>
-      <c r="I81" s="1">
-        <v>100</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A82" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C82" s="1"/>
-      <c r="D82" s="2">
-        <v>46507</v>
-      </c>
-      <c r="E82" s="3">
-        <v>9.1300000000000006E-2</v>
-      </c>
       <c r="F82" s="1">
         <v>2</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H82" s="1">
         <v>100</v>
@@ -3490,17 +3545,16 @@
     </row>
     <row r="83" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C83" s="1"/>
       <c r="D83" s="2">
-        <v>47292</v>
+        <v>46092</v>
       </c>
       <c r="E83" s="3">
-        <v>0.08</v>
+        <v>7.4899999999999994E-2</v>
       </c>
       <c r="F83" s="1">
         <v>2</v>
@@ -3523,23 +3577,22 @@
     </row>
     <row r="84" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C84" s="1"/>
       <c r="D84" s="2">
-        <v>47299</v>
+        <v>46170</v>
       </c>
       <c r="E84" s="3">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="F84" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H84" s="1">
         <v>100</v>
@@ -3555,21 +3608,21 @@
       </c>
     </row>
     <row r="85" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A85" s="1" t="s">
-        <v>101</v>
+      <c r="A85" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="2">
-        <v>47686</v>
+        <v>46186</v>
       </c>
       <c r="E85" s="3">
-        <v>8.7499999999999994E-2</v>
+        <v>0.06</v>
       </c>
       <c r="F85" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>20</v>
@@ -3589,16 +3642,17 @@
     </row>
     <row r="86" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="C86" s="1"/>
       <c r="D86" s="2">
-        <v>48047</v>
+        <v>46348</v>
       </c>
       <c r="E86" s="3">
-        <v>9.7000000000000003E-2</v>
+        <v>9.7500000000000003E-2</v>
       </c>
       <c r="F86" s="1">
         <v>2</v>
@@ -3621,23 +3675,23 @@
     </row>
     <row r="87" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="2">
-        <v>48102</v>
+        <v>46683</v>
       </c>
       <c r="E87" s="3">
-        <v>8.7499999999999994E-2</v>
+        <v>5.7500000000000002E-2</v>
       </c>
       <c r="F87" s="1">
         <v>2</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H87" s="1">
         <v>100</v>
@@ -3653,17 +3707,18 @@
       </c>
     </row>
     <row r="88" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A88" s="1" t="s">
-        <v>104</v>
+      <c r="A88" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="C88" s="1"/>
       <c r="D88" s="2">
-        <v>48364</v>
+        <v>47070</v>
       </c>
       <c r="E88" s="3">
-        <v>8.5000000000000006E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="F88" s="1">
         <v>2</v>
@@ -3686,22 +3741,23 @@
     </row>
     <row r="89" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="C89" s="1"/>
       <c r="D89" s="2">
-        <v>48503</v>
+        <v>47388</v>
       </c>
       <c r="E89" s="3">
-        <v>7.8799999999999995E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F89" s="1">
         <v>2</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H89" s="1">
         <v>100</v>
@@ -3717,23 +3773,24 @@
       </c>
     </row>
     <row r="90" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A90" s="1" t="s">
-        <v>106</v>
+      <c r="A90" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="C90" s="1"/>
       <c r="D90" s="2">
-        <v>48740</v>
+        <v>47414</v>
       </c>
       <c r="E90" s="3">
-        <v>8.5000000000000006E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
       <c r="F90" s="1">
         <v>2</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H90" s="1">
         <v>100</v>
@@ -3748,24 +3805,24 @@
         <v>121</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="6" t="s">
-        <v>107</v>
+    <row r="91" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D91" s="2">
-        <v>48852</v>
+        <v>47357</v>
       </c>
       <c r="E91" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="F91" s="1">
         <v>2</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H91" s="1">
         <v>100</v>
@@ -3781,18 +3838,17 @@
       </c>
     </row>
     <row r="92" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A92" s="1" t="s">
-        <v>108</v>
+      <c r="A92" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C92" s="1"/>
       <c r="D92" s="2">
-        <v>49399</v>
+        <v>48131</v>
       </c>
       <c r="E92" s="3">
-        <v>0.08</v>
+        <v>7.6499999999999999E-2</v>
       </c>
       <c r="F92" s="1">
         <v>2</v>
@@ -3815,17 +3871,17 @@
     </row>
     <row r="93" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="2">
-        <v>49653</v>
+        <v>48165</v>
       </c>
       <c r="E93" s="3">
-        <v>7.6300000000000007E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
       <c r="F93" s="1">
         <v>2</v>
@@ -3847,18 +3903,18 @@
       </c>
     </row>
     <row r="94" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A94" s="6" t="s">
-        <v>110</v>
+      <c r="A94" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="2">
-        <v>48961</v>
+        <v>48727</v>
       </c>
       <c r="E94" s="3">
-        <v>8.7499999999999994E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="F94" s="1">
         <v>2</v>
@@ -3880,57 +3936,502 @@
       </c>
     </row>
     <row r="95" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A95" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C95" s="1"/>
+      <c r="D95" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E95" s="3">
+        <v>0.1095</v>
+      </c>
+      <c r="F95" s="1">
+        <v>4</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H95" s="1">
+        <v>100</v>
+      </c>
+      <c r="I95" s="1">
+        <v>100</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="96" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A96" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C96" s="1"/>
-    </row>
-    <row r="97" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D96" s="2">
+        <v>46221</v>
+      </c>
+      <c r="E96" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="F96" s="1">
+        <v>2</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H96" s="1">
+        <v>100</v>
+      </c>
+      <c r="I96" s="1">
+        <v>100</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C97" s="1"/>
-    </row>
-    <row r="98" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D97" s="2">
+        <v>46507</v>
+      </c>
+      <c r="E97" s="3">
+        <v>9.1300000000000006E-2</v>
+      </c>
+      <c r="F97" s="1">
+        <v>2</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H97" s="1">
+        <v>100</v>
+      </c>
+      <c r="I97" s="1">
+        <v>100</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C98" s="1"/>
-    </row>
-    <row r="99" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D98" s="2">
+        <v>47292</v>
+      </c>
+      <c r="E98" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="F98" s="1">
+        <v>2</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H98" s="1">
+        <v>100</v>
+      </c>
+      <c r="I98" s="1">
+        <v>100</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A99" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C99" s="1"/>
-    </row>
-    <row r="100" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D99" s="2">
+        <v>47299</v>
+      </c>
+      <c r="E99" s="3">
+        <v>0.09</v>
+      </c>
+      <c r="F99" s="1">
+        <v>2</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H99" s="1">
+        <v>100</v>
+      </c>
+      <c r="I99" s="1">
+        <v>100</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C100" s="1"/>
-    </row>
-    <row r="101" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C101" s="1"/>
-    </row>
-    <row r="102" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D100" s="2">
+        <v>47686</v>
+      </c>
+      <c r="E100" s="3">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="F100" s="1">
+        <v>2</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H100" s="1">
+        <v>100</v>
+      </c>
+      <c r="I100" s="1">
+        <v>100</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A101" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D101" s="2">
+        <v>48047</v>
+      </c>
+      <c r="E101" s="3">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="F101" s="1">
+        <v>2</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H101" s="1">
+        <v>100</v>
+      </c>
+      <c r="I101" s="1">
+        <v>100</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A102" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C102" s="1"/>
-    </row>
-    <row r="103" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C103" s="1"/>
-    </row>
-    <row r="104" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C104" s="1"/>
-    </row>
-    <row r="105" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C105" s="1"/>
-    </row>
-    <row r="106" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C106" s="1"/>
-    </row>
-    <row r="107" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D102" s="2">
+        <v>48102</v>
+      </c>
+      <c r="E102" s="3">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="F102" s="1">
+        <v>2</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H102" s="1">
+        <v>100</v>
+      </c>
+      <c r="I102" s="1">
+        <v>100</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D103" s="2">
+        <v>48364</v>
+      </c>
+      <c r="E103" s="3">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="F103" s="1">
+        <v>2</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H103" s="1">
+        <v>100</v>
+      </c>
+      <c r="I103" s="1">
+        <v>100</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A104" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D104" s="2">
+        <v>48503</v>
+      </c>
+      <c r="E104" s="3">
+        <v>7.8799999999999995E-2</v>
+      </c>
+      <c r="F104" s="1">
+        <v>2</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H104" s="1">
+        <v>100</v>
+      </c>
+      <c r="I104" s="1">
+        <v>100</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D105" s="2">
+        <v>48740</v>
+      </c>
+      <c r="E105" s="3">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="F105" s="1">
+        <v>2</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H105" s="1">
+        <v>100</v>
+      </c>
+      <c r="I105" s="1">
+        <v>100</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D106" s="2">
+        <v>48852</v>
+      </c>
+      <c r="E106" s="3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F106" s="1">
+        <v>2</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H106" s="1">
+        <v>100</v>
+      </c>
+      <c r="I106" s="1">
+        <v>100</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C107" s="1"/>
-    </row>
-    <row r="108" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D107" s="2">
+        <v>49399</v>
+      </c>
+      <c r="E107" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="F107" s="1">
+        <v>2</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H107" s="1">
+        <v>100</v>
+      </c>
+      <c r="I107" s="1">
+        <v>100</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A108" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C108" s="1"/>
-    </row>
-    <row r="109" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D108" s="2">
+        <v>49653</v>
+      </c>
+      <c r="E108" s="3">
+        <v>7.6300000000000007E-2</v>
+      </c>
+      <c r="F108" s="1">
+        <v>2</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H108" s="1">
+        <v>100</v>
+      </c>
+      <c r="I108" s="1">
+        <v>100</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A109" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C109" s="1"/>
-    </row>
-    <row r="110" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D109" s="2">
+        <v>48961</v>
+      </c>
+      <c r="E109" s="3">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="F109" s="1">
+        <v>2</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H109" s="1">
+        <v>100</v>
+      </c>
+      <c r="I109" s="1">
+        <v>100</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C110" s="1"/>
     </row>
-    <row r="111" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C111" s="1"/>
     </row>
-    <row r="112" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C112" s="1"/>
     </row>
     <row r="113" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
@@ -4071,8 +4572,6 @@
     <row r="158" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C158" s="1"/>
     </row>
-    <row r="1048575" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1048576" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/SPR_BS_master.xlsx
+++ b/data/SPR_BS_master.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\SPR-BS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9928067-7160-4DEE-89B9-8B8787C7083D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062BC834-93BC-4043-A31D-F54299EA0F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="master_bono" sheetId="1" r:id="rId1"/>
-    <sheet name="README" sheetId="2" r:id="rId2"/>
+    <sheet name="equivalencias" sheetId="3" r:id="rId2"/>
+    <sheet name="README" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="280">
   <si>
     <t>codigo</t>
   </si>
@@ -438,9 +439,6 @@
     <t>S30N6</t>
   </si>
   <si>
-    <t>T13F6</t>
-  </si>
-  <si>
     <t>BONCAP</t>
   </si>
   <si>
@@ -457,6 +455,429 @@
   </si>
   <si>
     <t>T30J7</t>
+  </si>
+  <si>
+    <t>MEP</t>
+  </si>
+  <si>
+    <t>CCL</t>
+  </si>
+  <si>
+    <t>MONEDA_FLUJO</t>
+  </si>
+  <si>
+    <t>TO26D</t>
+  </si>
+  <si>
+    <t>TO26C</t>
+  </si>
+  <si>
+    <t>TY30D</t>
+  </si>
+  <si>
+    <t>TY30C</t>
+  </si>
+  <si>
+    <t>TX26D</t>
+  </si>
+  <si>
+    <t>TX26C</t>
+  </si>
+  <si>
+    <t>TX28D</t>
+  </si>
+  <si>
+    <t>TX28C</t>
+  </si>
+  <si>
+    <t>TX31D</t>
+  </si>
+  <si>
+    <t>TX31C</t>
+  </si>
+  <si>
+    <t>TZX6D</t>
+  </si>
+  <si>
+    <t>TZX6C</t>
+  </si>
+  <si>
+    <t>XL6D</t>
+  </si>
+  <si>
+    <t>XL6C</t>
+  </si>
+  <si>
+    <t>TZX7D</t>
+  </si>
+  <si>
+    <t>TZX7C</t>
+  </si>
+  <si>
+    <t>TZX8D</t>
+  </si>
+  <si>
+    <t>TZX8C</t>
+  </si>
+  <si>
+    <t>TXD6D</t>
+  </si>
+  <si>
+    <t>TXD7D</t>
+  </si>
+  <si>
+    <t>TXD6C</t>
+  </si>
+  <si>
+    <t>TXD7C</t>
+  </si>
+  <si>
+    <t>TXM6D</t>
+  </si>
+  <si>
+    <t>TXM6C</t>
+  </si>
+  <si>
+    <t>TXM7D</t>
+  </si>
+  <si>
+    <t>TXM7C</t>
+  </si>
+  <si>
+    <t>TXO6D</t>
+  </si>
+  <si>
+    <t>TXO6C</t>
+  </si>
+  <si>
+    <t>DA6D</t>
+  </si>
+  <si>
+    <t>DA6C</t>
+  </si>
+  <si>
+    <t>SF6D</t>
+  </si>
+  <si>
+    <t>SF6C</t>
+  </si>
+  <si>
+    <t>S2A6D</t>
+  </si>
+  <si>
+    <t>S2A6C</t>
+  </si>
+  <si>
+    <t>SM6D</t>
+  </si>
+  <si>
+    <t>SM6C</t>
+  </si>
+  <si>
+    <t>SA6D</t>
+  </si>
+  <si>
+    <t>SA6C</t>
+  </si>
+  <si>
+    <t>SY6D</t>
+  </si>
+  <si>
+    <t>SY6C</t>
+  </si>
+  <si>
+    <t>SL6D</t>
+  </si>
+  <si>
+    <t>SL6C</t>
+  </si>
+  <si>
+    <t>SG6D</t>
+  </si>
+  <si>
+    <t>SG6C</t>
+  </si>
+  <si>
+    <t>SO6D</t>
+  </si>
+  <si>
+    <t>SO6C</t>
+  </si>
+  <si>
+    <t>SN6D</t>
+  </si>
+  <si>
+    <t>SN6C</t>
+  </si>
+  <si>
+    <t>TJ6D</t>
+  </si>
+  <si>
+    <t>TJ6C</t>
+  </si>
+  <si>
+    <t>TE7D</t>
+  </si>
+  <si>
+    <t>TA7D</t>
+  </si>
+  <si>
+    <t>TY7D</t>
+  </si>
+  <si>
+    <t>TJ7D</t>
+  </si>
+  <si>
+    <t>TE7C</t>
+  </si>
+  <si>
+    <t>TA7C</t>
+  </si>
+  <si>
+    <t>TY7C</t>
+  </si>
+  <si>
+    <t>TJ7C</t>
+  </si>
+  <si>
+    <t>BC28D</t>
+  </si>
+  <si>
+    <t>BC28C</t>
+  </si>
+  <si>
+    <t>CO32D</t>
+  </si>
+  <si>
+    <t>CO32C</t>
+  </si>
+  <si>
+    <t>BB7DC</t>
+  </si>
+  <si>
+    <t>BA7DC</t>
+  </si>
+  <si>
+    <t>CS38D</t>
+  </si>
+  <si>
+    <t>LOC3D</t>
+  </si>
+  <si>
+    <t>YMCVD</t>
+  </si>
+  <si>
+    <t>LMS9D</t>
+  </si>
+  <si>
+    <t>DNC3D</t>
+  </si>
+  <si>
+    <t>IRCND</t>
+  </si>
+  <si>
+    <t>PN37D</t>
+  </si>
+  <si>
+    <t>PN35D</t>
+  </si>
+  <si>
+    <t>IRCOD</t>
+  </si>
+  <si>
+    <t>PN41D</t>
+  </si>
+  <si>
+    <t>VSCRD</t>
+  </si>
+  <si>
+    <t>PN36D</t>
+  </si>
+  <si>
+    <t>TLCPD</t>
+  </si>
+  <si>
+    <t>MTCGD</t>
+  </si>
+  <si>
+    <t>TLC1D</t>
+  </si>
+  <si>
+    <t>PNDCD</t>
+  </si>
+  <si>
+    <t>BACGD</t>
+  </si>
+  <si>
+    <t>YMCID</t>
+  </si>
+  <si>
+    <t>YM39D</t>
+  </si>
+  <si>
+    <t>TLCMD</t>
+  </si>
+  <si>
+    <t>YMCXD</t>
+  </si>
+  <si>
+    <t>PLC4D</t>
+  </si>
+  <si>
+    <t>YFCJD</t>
+  </si>
+  <si>
+    <t>VSCVD</t>
+  </si>
+  <si>
+    <t>YMCJD</t>
+  </si>
+  <si>
+    <t>IRCPD</t>
+  </si>
+  <si>
+    <t>VSCTD</t>
+  </si>
+  <si>
+    <t>YM34D</t>
+  </si>
+  <si>
+    <t>CS38C</t>
+  </si>
+  <si>
+    <t>LOC3C</t>
+  </si>
+  <si>
+    <t>YMCVC</t>
+  </si>
+  <si>
+    <t>LMS9C</t>
+  </si>
+  <si>
+    <t>DNC3C</t>
+  </si>
+  <si>
+    <t>IRCNC</t>
+  </si>
+  <si>
+    <t>PN37C</t>
+  </si>
+  <si>
+    <t>PN35C</t>
+  </si>
+  <si>
+    <t>IRCOC</t>
+  </si>
+  <si>
+    <t>PN41C</t>
+  </si>
+  <si>
+    <t>VSCRC</t>
+  </si>
+  <si>
+    <t>PN36C</t>
+  </si>
+  <si>
+    <t>TLCPC</t>
+  </si>
+  <si>
+    <t>MTCGC</t>
+  </si>
+  <si>
+    <t>TLC1C</t>
+  </si>
+  <si>
+    <t>PNDCC</t>
+  </si>
+  <si>
+    <t>BACGC</t>
+  </si>
+  <si>
+    <t>YMCIC</t>
+  </si>
+  <si>
+    <t>YM39C</t>
+  </si>
+  <si>
+    <t>TLCMC</t>
+  </si>
+  <si>
+    <t>YMCXC</t>
+  </si>
+  <si>
+    <t>PLC4C</t>
+  </si>
+  <si>
+    <t>YFCJC</t>
+  </si>
+  <si>
+    <t>VSCVC</t>
+  </si>
+  <si>
+    <t>YMCJC</t>
+  </si>
+  <si>
+    <t>IRCPC</t>
+  </si>
+  <si>
+    <t>VSCTC</t>
+  </si>
+  <si>
+    <t>YM34C</t>
+  </si>
+  <si>
+    <t>PARPD</t>
+  </si>
+  <si>
+    <t>DICPD</t>
+  </si>
+  <si>
+    <t>CUAPD</t>
+  </si>
+  <si>
+    <t>PARPC</t>
+  </si>
+  <si>
+    <t>DICPC</t>
+  </si>
+  <si>
+    <t>CUAPC</t>
+  </si>
+  <si>
+    <t>AL29C</t>
+  </si>
+  <si>
+    <t>AN29C</t>
+  </si>
+  <si>
+    <t>AL30C</t>
+  </si>
+  <si>
+    <t>AL35C</t>
+  </si>
+  <si>
+    <t>AE38C</t>
+  </si>
+  <si>
+    <t>AL41C</t>
+  </si>
+  <si>
+    <t>GD29C</t>
+  </si>
+  <si>
+    <t>GD30C</t>
+  </si>
+  <si>
+    <t>GD35C</t>
+  </si>
+  <si>
+    <t>GD38C</t>
+  </si>
+  <si>
+    <t>GD41C</t>
+  </si>
+  <si>
+    <t>GD46C</t>
   </si>
 </sst>
 </file>
@@ -543,7 +964,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -572,11 +993,25 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -768,7 +1203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K158"/>
+  <dimension ref="A1:K157"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="15.33203125" style="1" customWidth="1"/>
@@ -2634,14 +3069,14 @@
     </row>
     <row r="55" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="2">
-        <v>46066</v>
+        <v>46203</v>
       </c>
       <c r="E55" s="3">
         <v>0</v>
@@ -2662,7 +3097,7 @@
         <v>11</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
@@ -2674,7 +3109,7 @@
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="2">
-        <v>46203</v>
+        <v>46402</v>
       </c>
       <c r="E56" s="3">
         <v>0</v>
@@ -2695,7 +3130,7 @@
         <v>11</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
@@ -2707,7 +3142,7 @@
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="2">
-        <v>46402</v>
+        <v>46507</v>
       </c>
       <c r="E57" s="3">
         <v>0</v>
@@ -2728,7 +3163,7 @@
         <v>11</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
@@ -2740,7 +3175,7 @@
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="2">
-        <v>46507</v>
+        <v>46538</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -2761,7 +3196,7 @@
         <v>11</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
@@ -2773,7 +3208,7 @@
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="2">
-        <v>46538</v>
+        <v>46568</v>
       </c>
       <c r="E59" s="3">
         <v>0</v>
@@ -2794,28 +3229,30 @@
         <v>11</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A60" s="1" t="s">
-        <v>139</v>
+      <c r="A60" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C60" s="1"/>
+      <c r="C60" s="2">
+        <v>45296</v>
+      </c>
       <c r="D60" s="2">
-        <v>46568</v>
+        <v>46691</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="F60" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H60" s="1">
         <v>100</v>
@@ -2827,18 +3264,18 @@
         <v>11</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A61" s="8" t="s">
-        <v>60</v>
+      <c r="A61" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="2">
-        <v>45296</v>
+        <v>45596</v>
       </c>
       <c r="D61" s="2">
         <v>46691</v>
@@ -2867,13 +3304,10 @@
     </row>
     <row r="62" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="C62" s="2">
-        <v>45596</v>
       </c>
       <c r="D62" s="2">
         <v>46691</v>
@@ -2902,10 +3336,13 @@
     </row>
     <row r="63" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="C63" s="2">
+        <v>45352</v>
       </c>
       <c r="D63" s="2">
         <v>46691</v>
@@ -2934,13 +3371,10 @@
     </row>
     <row r="64" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C64" s="2">
-        <v>45352</v>
+        <v>65</v>
       </c>
       <c r="D64" s="2">
         <v>46691</v>
@@ -2961,7 +3395,7 @@
         <v>100</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="K64" s="1" t="s">
         <v>122</v>
@@ -2969,7 +3403,7 @@
     </row>
     <row r="65" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>65</v>
@@ -3001,7 +3435,7 @@
     </row>
     <row r="66" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>65</v>
@@ -3033,7 +3467,7 @@
     </row>
     <row r="67" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>65</v>
@@ -3064,11 +3498,11 @@
       </c>
     </row>
     <row r="68" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
-        <v>68</v>
+      <c r="A68" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="D68" s="2">
         <v>46691</v>
@@ -3089,7 +3523,7 @@
         <v>100</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K68" s="1" t="s">
         <v>122</v>
@@ -3097,7 +3531,7 @@
     </row>
     <row r="69" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>18</v>
@@ -3129,7 +3563,7 @@
     </row>
     <row r="70" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>18</v>
@@ -3161,7 +3595,7 @@
     </row>
     <row r="71" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>18</v>
@@ -3192,20 +3626,20 @@
       </c>
     </row>
     <row r="72" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A72" s="9" t="s">
-        <v>73</v>
+      <c r="A72" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D72" s="2">
-        <v>46691</v>
+        <v>46173</v>
       </c>
       <c r="E72" s="3">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="F72" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>12</v>
@@ -3214,21 +3648,21 @@
         <v>100</v>
       </c>
       <c r="I72" s="1">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="K72" s="1" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A73" s="1" t="s">
-        <v>74</v>
+      <c r="A73" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D73" s="2">
         <v>46173</v>
@@ -3249,18 +3683,18 @@
         <v>67</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="K73" s="1" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A74" s="9" t="s">
-        <v>75</v>
+      <c r="A74" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="D74" s="2">
         <v>46173</v>
@@ -3281,7 +3715,7 @@
         <v>67</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="K74" s="1" t="s">
         <v>122</v>
@@ -3289,31 +3723,31 @@
     </row>
     <row r="75" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="D75" s="2">
-        <v>46173</v>
+        <v>46805</v>
       </c>
       <c r="E75" s="3">
-        <v>0.03</v>
+        <v>0.35920000000000002</v>
       </c>
       <c r="F75" s="1">
         <v>4</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H75" s="1">
         <v>100</v>
       </c>
       <c r="I75" s="1">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="K75" s="1" t="s">
         <v>122</v>
@@ -3321,22 +3755,22 @@
     </row>
     <row r="76" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D76" s="2">
-        <v>46805</v>
+        <v>48397</v>
       </c>
       <c r="E76" s="3">
-        <v>0.35920000000000002</v>
+        <v>6.6299999999999998E-2</v>
       </c>
       <c r="F76" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H76" s="1">
         <v>100</v>
@@ -3345,7 +3779,7 @@
         <v>100</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K76" s="1" t="s">
         <v>122</v>
@@ -3353,16 +3787,16 @@
     </row>
     <row r="77" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D77" s="2">
-        <v>48397</v>
+        <v>50284</v>
       </c>
       <c r="E77" s="3">
-        <v>6.6299999999999998E-2</v>
+        <v>5.8799999999999998E-2</v>
       </c>
       <c r="F77" s="1">
         <v>2</v>
@@ -3377,7 +3811,7 @@
         <v>100</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K77" s="1" t="s">
         <v>122</v>
@@ -3385,16 +3819,16 @@
     </row>
     <row r="78" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>11</v>
+        <v>80</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="D78" s="2">
         <v>50284</v>
       </c>
       <c r="E78" s="3">
-        <v>5.8799999999999998E-2</v>
+        <v>6.6299999999999998E-2</v>
       </c>
       <c r="F78" s="1">
         <v>2</v>
@@ -3406,7 +3840,7 @@
         <v>100</v>
       </c>
       <c r="I78" s="1">
-        <v>100</v>
+        <v>91.84</v>
       </c>
       <c r="J78" s="1" t="s">
         <v>11</v>
@@ -3416,10 +3850,10 @@
       </c>
     </row>
     <row r="79" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A79" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B79" s="7" t="s">
+      <c r="A79" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D79" s="2">
@@ -3441,15 +3875,15 @@
         <v>91.84</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K79" s="1" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A80" s="9" t="s">
-        <v>81</v>
+      <c r="A80" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>18</v>
@@ -3458,7 +3892,7 @@
         <v>50284</v>
       </c>
       <c r="E80" s="3">
-        <v>6.6299999999999998E-2</v>
+        <v>5.8799999999999998E-2</v>
       </c>
       <c r="F80" s="1">
         <v>2</v>
@@ -3470,7 +3904,7 @@
         <v>100</v>
       </c>
       <c r="I80" s="1">
-        <v>91.84</v>
+        <v>100</v>
       </c>
       <c r="J80" s="1" t="s">
         <v>18</v>
@@ -3480,23 +3914,23 @@
       </c>
     </row>
     <row r="81" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A81" s="1" t="s">
-        <v>82</v>
+      <c r="A81" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D81" s="2">
-        <v>50284</v>
+        <v>46084</v>
       </c>
       <c r="E81" s="3">
-        <v>5.8799999999999998E-2</v>
+        <v>0.08</v>
       </c>
       <c r="F81" s="1">
         <v>2</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H81" s="1">
         <v>100</v>
@@ -3505,24 +3939,24 @@
         <v>100</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A82" s="6" t="s">
-        <v>83</v>
+      <c r="A82" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D82" s="2">
-        <v>46084</v>
+        <v>46092</v>
       </c>
       <c r="E82" s="3">
-        <v>0.08</v>
+        <v>7.4899999999999994E-2</v>
       </c>
       <c r="F82" s="1">
         <v>2</v>
@@ -3544,20 +3978,20 @@
       </c>
     </row>
     <row r="83" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A83" s="1" t="s">
-        <v>84</v>
+      <c r="A83" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D83" s="2">
-        <v>46092</v>
+        <v>46170</v>
       </c>
       <c r="E83" s="3">
-        <v>7.4899999999999994E-2</v>
+        <v>0.06</v>
       </c>
       <c r="F83" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>20</v>
@@ -3577,13 +4011,14 @@
     </row>
     <row r="84" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="C84" s="1"/>
       <c r="D84" s="2">
-        <v>46170</v>
+        <v>46186</v>
       </c>
       <c r="E84" s="3">
         <v>0.06</v>
@@ -3609,20 +4044,20 @@
     </row>
     <row r="85" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="2">
-        <v>46186</v>
+        <v>46348</v>
       </c>
       <c r="E85" s="3">
-        <v>0.06</v>
+        <v>9.7500000000000003E-2</v>
       </c>
       <c r="F85" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>20</v>
@@ -3642,17 +4077,17 @@
     </row>
     <row r="86" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="2">
-        <v>46348</v>
+        <v>46683</v>
       </c>
       <c r="E86" s="3">
-        <v>9.7500000000000003E-2</v>
+        <v>5.7500000000000002E-2</v>
       </c>
       <c r="F86" s="1">
         <v>2</v>
@@ -3675,17 +4110,17 @@
     </row>
     <row r="87" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="2">
-        <v>46683</v>
+        <v>47070</v>
       </c>
       <c r="E87" s="3">
-        <v>5.7500000000000002E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="F87" s="1">
         <v>2</v>
@@ -3708,17 +4143,17 @@
     </row>
     <row r="88" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C88" s="1"/>
       <c r="D88" s="2">
-        <v>47070</v>
+        <v>47388</v>
       </c>
       <c r="E88" s="3">
-        <v>6.25E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F88" s="1">
         <v>2</v>
@@ -3741,17 +4176,17 @@
     </row>
     <row r="89" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C89" s="1"/>
       <c r="D89" s="2">
-        <v>47388</v>
+        <v>47414</v>
       </c>
       <c r="E89" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
       <c r="F89" s="1">
         <v>2</v>
@@ -3773,18 +4208,17 @@
       </c>
     </row>
     <row r="90" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A90" s="6" t="s">
-        <v>91</v>
+      <c r="A90" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C90" s="1"/>
       <c r="D90" s="2">
-        <v>47414</v>
+        <v>47357</v>
       </c>
       <c r="E90" s="3">
-        <v>7.2499999999999995E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="F90" s="1">
         <v>2</v>
@@ -3806,17 +4240,17 @@
       </c>
     </row>
     <row r="91" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A91" s="1" t="s">
-        <v>92</v>
+      <c r="A91" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D91" s="2">
-        <v>47357</v>
+        <v>48131</v>
       </c>
       <c r="E91" s="3">
-        <v>7.4999999999999997E-2</v>
+        <v>7.6499999999999999E-2</v>
       </c>
       <c r="F91" s="1">
         <v>2</v>
@@ -3839,16 +4273,17 @@
     </row>
     <row r="92" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="C92" s="1"/>
       <c r="D92" s="2">
-        <v>48131</v>
+        <v>48165</v>
       </c>
       <c r="E92" s="3">
-        <v>7.6499999999999999E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
       <c r="F92" s="1">
         <v>2</v>
@@ -3870,24 +4305,24 @@
       </c>
     </row>
     <row r="93" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A93" s="6" t="s">
-        <v>94</v>
+      <c r="A93" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="2">
-        <v>48165</v>
+        <v>48727</v>
       </c>
       <c r="E93" s="3">
-        <v>7.2499999999999995E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="F93" s="1">
         <v>2</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H93" s="1">
         <v>100</v>
@@ -3903,24 +4338,24 @@
       </c>
     </row>
     <row r="94" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A94" s="1" t="s">
-        <v>95</v>
+      <c r="A94" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="2">
-        <v>48727</v>
+        <v>46203</v>
       </c>
       <c r="E94" s="3">
-        <v>9.5000000000000001E-2</v>
+        <v>0.1095</v>
       </c>
       <c r="F94" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H94" s="1">
         <v>100</v>
@@ -3937,20 +4372,20 @@
     </row>
     <row r="95" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="2">
-        <v>46203</v>
+        <v>46221</v>
       </c>
       <c r="E95" s="3">
-        <v>0.1095</v>
+        <v>0.08</v>
       </c>
       <c r="F95" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>20</v>
@@ -3969,24 +4404,24 @@
       </c>
     </row>
     <row r="96" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A96" s="6" t="s">
-        <v>97</v>
+      <c r="A96" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="2">
-        <v>46221</v>
+        <v>46507</v>
       </c>
       <c r="E96" s="3">
-        <v>0.08</v>
+        <v>9.1300000000000006E-2</v>
       </c>
       <c r="F96" s="1">
         <v>2</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H96" s="1">
         <v>100</v>
@@ -4003,23 +4438,23 @@
     </row>
     <row r="97" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="2">
-        <v>46507</v>
+        <v>47292</v>
       </c>
       <c r="E97" s="3">
-        <v>9.1300000000000006E-2</v>
+        <v>0.08</v>
       </c>
       <c r="F97" s="1">
         <v>2</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H97" s="1">
         <v>100</v>
@@ -4035,24 +4470,24 @@
       </c>
     </row>
     <row r="98" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A98" s="1" t="s">
-        <v>99</v>
+      <c r="A98" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="2">
-        <v>47292</v>
+        <v>47299</v>
       </c>
       <c r="E98" s="3">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="F98" s="1">
         <v>2</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H98" s="1">
         <v>100</v>
@@ -4068,24 +4503,24 @@
       </c>
     </row>
     <row r="99" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A99" s="6" t="s">
-        <v>100</v>
+      <c r="A99" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C99" s="1"/>
       <c r="D99" s="2">
-        <v>47299</v>
+        <v>47686</v>
       </c>
       <c r="E99" s="3">
-        <v>0.09</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="F99" s="1">
         <v>2</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H99" s="1">
         <v>100</v>
@@ -4101,18 +4536,17 @@
       </c>
     </row>
     <row r="100" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A100" s="1" t="s">
-        <v>101</v>
+      <c r="A100" s="6" t="s">
+        <v>102</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C100" s="1"/>
       <c r="D100" s="2">
-        <v>47686</v>
+        <v>48047</v>
       </c>
       <c r="E100" s="3">
-        <v>8.7499999999999994E-2</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="F100" s="1">
         <v>2</v>
@@ -4135,22 +4569,23 @@
     </row>
     <row r="101" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="C101" s="1"/>
       <c r="D101" s="2">
-        <v>48047</v>
+        <v>48102</v>
       </c>
       <c r="E101" s="3">
-        <v>9.7000000000000003E-2</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="F101" s="1">
         <v>2</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H101" s="1">
         <v>100</v>
@@ -4166,24 +4601,23 @@
       </c>
     </row>
     <row r="102" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A102" s="6" t="s">
-        <v>103</v>
+      <c r="A102" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C102" s="1"/>
       <c r="D102" s="2">
-        <v>48102</v>
+        <v>48364</v>
       </c>
       <c r="E102" s="3">
-        <v>8.7499999999999994E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="F102" s="1">
         <v>2</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H102" s="1">
         <v>100</v>
@@ -4199,23 +4633,23 @@
       </c>
     </row>
     <row r="103" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A103" s="1" t="s">
-        <v>104</v>
+      <c r="A103" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D103" s="2">
-        <v>48364</v>
+        <v>48503</v>
       </c>
       <c r="E103" s="3">
-        <v>8.5000000000000006E-2</v>
+        <v>7.8799999999999995E-2</v>
       </c>
       <c r="F103" s="1">
         <v>2</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H103" s="1">
         <v>100</v>
@@ -4231,17 +4665,17 @@
       </c>
     </row>
     <row r="104" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A104" s="6" t="s">
-        <v>105</v>
+      <c r="A104" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D104" s="2">
-        <v>48503</v>
+        <v>48740</v>
       </c>
       <c r="E104" s="3">
-        <v>7.8799999999999995E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="F104" s="1">
         <v>2</v>
@@ -4262,18 +4696,18 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A105" s="1" t="s">
-        <v>106</v>
+    <row r="105" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="6" t="s">
+        <v>107</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D105" s="2">
-        <v>48740</v>
+        <v>48852</v>
       </c>
       <c r="E105" s="3">
-        <v>8.5000000000000006E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F105" s="1">
         <v>2</v>
@@ -4294,24 +4728,25 @@
         <v>121</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="6" t="s">
-        <v>107</v>
+    <row r="106" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="C106" s="1"/>
       <c r="D106" s="2">
-        <v>48852</v>
+        <v>49399</v>
       </c>
       <c r="E106" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="F106" s="1">
         <v>2</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H106" s="1">
         <v>100</v>
@@ -4327,18 +4762,18 @@
       </c>
     </row>
     <row r="107" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A107" s="1" t="s">
-        <v>108</v>
+      <c r="A107" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="2">
-        <v>49399</v>
+        <v>49653</v>
       </c>
       <c r="E107" s="3">
-        <v>0.08</v>
+        <v>7.6300000000000007E-2</v>
       </c>
       <c r="F107" s="1">
         <v>2</v>
@@ -4361,23 +4796,23 @@
     </row>
     <row r="108" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="2">
-        <v>49653</v>
+        <v>48961</v>
       </c>
       <c r="E108" s="3">
-        <v>7.6300000000000007E-2</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="F108" s="1">
         <v>2</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H108" s="1">
         <v>100</v>
@@ -4393,37 +4828,7 @@
       </c>
     </row>
     <row r="109" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A109" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="C109" s="1"/>
-      <c r="D109" s="2">
-        <v>48961</v>
-      </c>
-      <c r="E109" s="3">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="F109" s="1">
-        <v>2</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H109" s="1">
-        <v>100</v>
-      </c>
-      <c r="I109" s="1">
-        <v>100</v>
-      </c>
-      <c r="J109" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K109" s="1" t="s">
-        <v>121</v>
-      </c>
     </row>
     <row r="110" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C110" s="1"/>
@@ -4569,16 +4974,1195 @@
     <row r="157" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C157" s="1"/>
     </row>
-    <row r="158" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C158" s="1"/>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236E667D-0708-4136-8419-BAB12652721D}">
+  <dimension ref="A1:D84"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="11.5546875" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="C81" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B82" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B83" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B84" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/data/SPR_BS_master.xlsx
+++ b/data/SPR_BS_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\SPR-BS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062BC834-93BC-4043-A31D-F54299EA0F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1632463D-F4B9-4C33-B754-C0BE0558CCB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="master_bono" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="285">
   <si>
     <t>codigo</t>
   </si>
@@ -878,6 +878,21 @@
   </si>
   <si>
     <t>GD46C</t>
+  </si>
+  <si>
+    <t>emisor</t>
+  </si>
+  <si>
+    <t>sector</t>
+  </si>
+  <si>
+    <t>legislacion</t>
+  </si>
+  <si>
+    <t>rating</t>
+  </si>
+  <si>
+    <t>tipo_tasa</t>
   </si>
 </sst>
 </file>
@@ -1203,7 +1218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K157"/>
+  <dimension ref="A1:P157"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="15.33203125" style="1" customWidth="1"/>
@@ -1213,7 +1228,7 @@
     <col min="12" max="16384" width="8.21875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1247,8 +1262,23 @@
       <c r="K1" s="4" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="L1" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>10</v>
       </c>
@@ -1283,7 +1313,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>13</v>
       </c>
@@ -1318,7 +1348,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>14</v>
       </c>
@@ -1353,7 +1383,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>15</v>
       </c>
@@ -1388,7 +1418,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -1423,7 +1453,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>17</v>
       </c>
@@ -1458,7 +1488,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -1493,7 +1523,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -1528,7 +1558,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
@@ -1563,7 +1593,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>23</v>
       </c>
@@ -1598,7 +1628,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
@@ -1633,7 +1663,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>25</v>
       </c>
@@ -1668,7 +1698,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,7 +1733,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>27</v>
       </c>
@@ -1738,7 +1768,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>28</v>
       </c>

--- a/data/SPR_BS_master.xlsx
+++ b/data/SPR_BS_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\SPR-BS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1632463D-F4B9-4C33-B754-C0BE0558CCB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD8AF81-36A6-4FF8-8DF2-13DDCF18D8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="master_bono" sheetId="1" r:id="rId1"/>
@@ -1015,7 +1015,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5006,12 +5016,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data/SPR_BS_master.xlsx
+++ b/data/SPR_BS_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\SPR-BS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD8AF81-36A6-4FF8-8DF2-13DDCF18D8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F78FCB7A-8131-4164-9B31-989BA3C5CD18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="285">
   <si>
     <t>codigo</t>
   </si>
@@ -1015,7 +1015,187 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="20">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3955,7 +4135,7 @@
     </row>
     <row r="81" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>18</v>
@@ -3987,7 +4167,7 @@
     </row>
     <row r="82" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>84</v>
+        <v>207</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>18</v>
@@ -4019,7 +4199,7 @@
     </row>
     <row r="83" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
-        <v>85</v>
+        <v>208</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>18</v>
@@ -4051,7 +4231,7 @@
     </row>
     <row r="84" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
-        <v>86</v>
+        <v>209</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>18</v>
@@ -4084,7 +4264,7 @@
     </row>
     <row r="85" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
-        <v>87</v>
+        <v>210</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>18</v>
@@ -4117,7 +4297,7 @@
     </row>
     <row r="86" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
-        <v>88</v>
+        <v>211</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>18</v>
@@ -4150,7 +4330,7 @@
     </row>
     <row r="87" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
-        <v>89</v>
+        <v>212</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>18</v>
@@ -4183,7 +4363,7 @@
     </row>
     <row r="88" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
-        <v>90</v>
+        <v>213</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>18</v>
@@ -4216,7 +4396,7 @@
     </row>
     <row r="89" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
-        <v>91</v>
+        <v>214</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>18</v>
@@ -4249,7 +4429,7 @@
     </row>
     <row r="90" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>92</v>
+        <v>215</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>18</v>
@@ -4281,7 +4461,7 @@
     </row>
     <row r="91" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
-        <v>93</v>
+        <v>216</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>18</v>
@@ -4313,7 +4493,7 @@
     </row>
     <row r="92" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>18</v>
@@ -4346,7 +4526,7 @@
     </row>
     <row r="93" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>95</v>
+        <v>218</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>18</v>
@@ -4379,7 +4559,7 @@
     </row>
     <row r="94" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
-        <v>96</v>
+        <v>219</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>18</v>
@@ -4412,7 +4592,7 @@
     </row>
     <row r="95" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
-        <v>97</v>
+        <v>220</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>18</v>
@@ -4445,7 +4625,7 @@
     </row>
     <row r="96" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>98</v>
+        <v>221</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>18</v>
@@ -4478,7 +4658,7 @@
     </row>
     <row r="97" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>99</v>
+        <v>222</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>18</v>
@@ -4511,7 +4691,7 @@
     </row>
     <row r="98" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
-        <v>100</v>
+        <v>223</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>18</v>
@@ -4544,7 +4724,7 @@
     </row>
     <row r="99" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>101</v>
+        <v>224</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>18</v>
@@ -4577,7 +4757,7 @@
     </row>
     <row r="100" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
-        <v>102</v>
+        <v>225</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>18</v>
@@ -4609,7 +4789,7 @@
     </row>
     <row r="101" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
-        <v>103</v>
+        <v>226</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>18</v>
@@ -4642,7 +4822,7 @@
     </row>
     <row r="102" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>104</v>
+        <v>227</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>18</v>
@@ -4674,7 +4854,7 @@
     </row>
     <row r="103" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A103" s="6" t="s">
-        <v>105</v>
+        <v>228</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>18</v>
@@ -4706,7 +4886,7 @@
     </row>
     <row r="104" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>106</v>
+        <v>229</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>18</v>
@@ -4738,7 +4918,7 @@
     </row>
     <row r="105" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
-        <v>107</v>
+        <v>230</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>18</v>
@@ -4770,7 +4950,7 @@
     </row>
     <row r="106" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>108</v>
+        <v>231</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>18</v>
@@ -4803,7 +4983,7 @@
     </row>
     <row r="107" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A107" s="6" t="s">
-        <v>109</v>
+        <v>232</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>18</v>
@@ -4836,7 +5016,7 @@
     </row>
     <row r="108" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
-        <v>110</v>
+        <v>233</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>18</v>
@@ -5016,7 +5196,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="lessThan">
       <formula>TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5027,13 +5207,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236E667D-0708-4136-8419-BAB12652721D}">
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:R84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="11.5546875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>11</v>
       </c>
@@ -5046,8 +5226,50 @@
       <c r="D1" s="4" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>10</v>
       </c>
@@ -5060,8 +5282,38 @@
       <c r="D2" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" s="2">
+        <v>38680</v>
+      </c>
+      <c r="F2" s="2">
+        <v>50770</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1.77E-2</v>
+      </c>
+      <c r="H2" s="1">
+        <v>2</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="1">
+        <v>100</v>
+      </c>
+      <c r="K2" s="1">
+        <v>100</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>13</v>
       </c>
@@ -5074,8 +5326,38 @@
       <c r="D3" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" s="2">
+        <v>37986</v>
+      </c>
+      <c r="F3" s="2">
+        <v>48944</v>
+      </c>
+      <c r="G3" s="3">
+        <v>5.8299999999999998E-2</v>
+      </c>
+      <c r="H3" s="1">
+        <v>2</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="1">
+        <v>100</v>
+      </c>
+      <c r="K3" s="1">
+        <v>80</v>
+      </c>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>14</v>
       </c>
@@ -5088,16 +5370,76 @@
       <c r="D4" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" s="2">
+        <v>37986</v>
+      </c>
+      <c r="F4" s="2">
+        <v>53327</v>
+      </c>
+      <c r="G4" s="3">
+        <v>3.3099999999999997E-2</v>
+      </c>
+      <c r="H4" s="1">
+        <v>2</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="1">
+        <v>100</v>
+      </c>
+      <c r="K4" s="1">
+        <v>100</v>
+      </c>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" s="2">
+        <v>40177</v>
+      </c>
+      <c r="F5" s="2">
+        <v>50770</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1.77E-2</v>
+      </c>
+      <c r="H5" s="1">
+        <v>2</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="1">
+        <v>100</v>
+      </c>
+      <c r="K5" s="1">
+        <v>100</v>
+      </c>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>16</v>
       </c>
@@ -5110,8 +5452,38 @@
       <c r="D6" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" s="2">
+        <v>44081</v>
+      </c>
+      <c r="F6" s="2">
+        <v>47308</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="1">
+        <v>100</v>
+      </c>
+      <c r="K6" s="1">
+        <v>70</v>
+      </c>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -5124,8 +5496,33 @@
       <c r="D7" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" s="2">
+        <v>46007</v>
+      </c>
+      <c r="F7" s="2">
+        <v>47452</v>
+      </c>
+      <c r="G7" s="3">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="1">
+        <v>100</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>22</v>
       </c>
@@ -5138,8 +5535,33 @@
       <c r="D8" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" s="2">
+        <v>44081</v>
+      </c>
+      <c r="F8" s="2">
+        <v>47673</v>
+      </c>
+      <c r="G8" s="3">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="H8" s="1">
+        <v>2</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="1">
+        <v>100</v>
+      </c>
+      <c r="K8" s="1">
+        <v>72</v>
+      </c>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>24</v>
       </c>
@@ -5152,8 +5574,33 @@
       <c r="D9" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" s="2">
+        <v>44081</v>
+      </c>
+      <c r="F9" s="2">
+        <v>49499</v>
+      </c>
+      <c r="G9" s="3">
+        <v>4.1300000000000003E-2</v>
+      </c>
+      <c r="H9" s="1">
+        <v>2</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="1">
+        <v>100</v>
+      </c>
+      <c r="K9" s="1">
+        <v>100</v>
+      </c>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>26</v>
       </c>
@@ -5166,8 +5613,33 @@
       <c r="D10" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" s="2">
+        <v>44081</v>
+      </c>
+      <c r="F10" s="2">
+        <v>50414</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="H10" s="1">
+        <v>2</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="1">
+        <v>100</v>
+      </c>
+      <c r="K10" s="1">
+        <v>100</v>
+      </c>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>28</v>
       </c>
@@ -5180,8 +5652,33 @@
       <c r="D11" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11" s="2">
+        <v>44081</v>
+      </c>
+      <c r="F11" s="2">
+        <v>51691</v>
+      </c>
+      <c r="G11" s="3">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="H11" s="1">
+        <v>2</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" s="1">
+        <v>100</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
+      </c>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>30</v>
       </c>
@@ -5194,8 +5691,33 @@
       <c r="D12" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12" s="2">
+        <v>44081</v>
+      </c>
+      <c r="F12" s="2">
+        <v>47308</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="H12" s="1">
+        <v>2</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" s="1">
+        <v>100</v>
+      </c>
+      <c r="K12" s="1">
+        <v>70</v>
+      </c>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
         <v>32</v>
       </c>
@@ -5208,8 +5730,33 @@
       <c r="D13" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13" s="2">
+        <v>44081</v>
+      </c>
+      <c r="F13" s="2">
+        <v>47673</v>
+      </c>
+      <c r="G13" s="3">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="H13" s="1">
+        <v>2</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="1">
+        <v>100</v>
+      </c>
+      <c r="K13" s="1">
+        <v>72</v>
+      </c>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>34</v>
       </c>
@@ -5222,8 +5769,33 @@
       <c r="D14" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" s="2">
+        <v>44081</v>
+      </c>
+      <c r="F14" s="2">
+        <v>49499</v>
+      </c>
+      <c r="G14" s="3">
+        <v>4.1300000000000003E-2</v>
+      </c>
+      <c r="H14" s="1">
+        <v>2</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J14" s="1">
+        <v>100</v>
+      </c>
+      <c r="K14" s="1">
+        <v>100</v>
+      </c>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>36</v>
       </c>
@@ -5236,8 +5808,33 @@
       <c r="D15" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15" s="2">
+        <v>44081</v>
+      </c>
+      <c r="F15" s="2">
+        <v>49499</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="H15" s="1">
+        <v>2</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J15" s="1">
+        <v>100</v>
+      </c>
+      <c r="K15" s="1">
+        <v>100</v>
+      </c>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
         <v>38</v>
       </c>
@@ -5250,8 +5847,33 @@
       <c r="D16" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" s="2">
+        <v>44081</v>
+      </c>
+      <c r="F16" s="2">
+        <v>51691</v>
+      </c>
+      <c r="G16" s="3">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="H16" s="1">
+        <v>2</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" s="1">
+        <v>100</v>
+      </c>
+      <c r="K16" s="1">
+        <v>100</v>
+      </c>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>40</v>
       </c>
@@ -5264,8 +5886,33 @@
       <c r="D17" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" s="2">
+        <v>44081</v>
+      </c>
+      <c r="F17" s="2">
+        <v>53517</v>
+      </c>
+      <c r="G17" s="3">
+        <v>4.1300000000000003E-2</v>
+      </c>
+      <c r="H17" s="1">
+        <v>2</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" s="1">
+        <v>100</v>
+      </c>
+      <c r="K17" s="1">
+        <v>93.18</v>
+      </c>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
         <v>42</v>
       </c>
@@ -5278,8 +5925,33 @@
       <c r="D18" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18" s="2">
+        <v>42660</v>
+      </c>
+      <c r="F18" s="2">
+        <v>46313</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0.155</v>
+      </c>
+      <c r="H18" s="1">
+        <v>2</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="1">
+        <v>100</v>
+      </c>
+      <c r="K18" s="1">
+        <v>100</v>
+      </c>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>43</v>
       </c>
@@ -5292,8 +5964,31 @@
       <c r="D19" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" s="2"/>
+      <c r="F19" s="2">
+        <v>47633</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="H19" s="1">
+        <v>2</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="1">
+        <v>100</v>
+      </c>
+      <c r="K19" s="1">
+        <v>100</v>
+      </c>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>44</v>
       </c>
@@ -5306,8 +6001,33 @@
       <c r="D20" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E20" s="2">
+        <v>44078</v>
+      </c>
+      <c r="F20" s="2">
+        <v>46335</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="H20" s="1">
+        <v>2</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20" s="1">
+        <v>100</v>
+      </c>
+      <c r="K20" s="1">
+        <v>40</v>
+      </c>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>46</v>
       </c>
@@ -5320,8 +6040,31 @@
       <c r="D21" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E21" s="2"/>
+      <c r="F21" s="2">
+        <v>47066</v>
+      </c>
+      <c r="G21" s="3">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="H21" s="1">
+        <v>2</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21" s="1">
+        <v>100</v>
+      </c>
+      <c r="K21" s="1">
+        <v>60</v>
+      </c>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
         <v>47</v>
       </c>
@@ -5334,8 +6077,33 @@
       <c r="D22" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22" s="2">
+        <v>44712</v>
+      </c>
+      <c r="F22" s="2">
+        <v>48182</v>
+      </c>
+      <c r="G22" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="H22" s="1">
+        <v>2</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J22" s="1">
+        <v>100</v>
+      </c>
+      <c r="K22" s="1">
+        <v>100</v>
+      </c>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>48</v>
       </c>
@@ -5348,8 +6116,31 @@
       <c r="D23" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E23" s="2"/>
+      <c r="F23" s="2">
+        <v>46203</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="1">
+        <v>100</v>
+      </c>
+      <c r="K23" s="1">
+        <v>100</v>
+      </c>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
         <v>49</v>
       </c>
@@ -5362,8 +6153,31 @@
       <c r="D24" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E24" s="2"/>
+      <c r="F24" s="2">
+        <v>46234</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="1">
+        <v>100</v>
+      </c>
+      <c r="K24" s="1">
+        <v>100</v>
+      </c>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>50</v>
       </c>
@@ -5376,8 +6190,31 @@
       <c r="D25" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E25" s="2"/>
+      <c r="F25" s="2">
+        <v>46568</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="1">
+        <v>100</v>
+      </c>
+      <c r="K25" s="1">
+        <v>100</v>
+      </c>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>51</v>
       </c>
@@ -5390,8 +6227,33 @@
       <c r="D26" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E26" s="2">
+        <v>45323</v>
+      </c>
+      <c r="F26" s="2">
+        <v>46934</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="1">
+        <v>100</v>
+      </c>
+      <c r="K26" s="1">
+        <v>100</v>
+      </c>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>52</v>
       </c>
@@ -5404,8 +6266,33 @@
       <c r="D27" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E27" s="2">
+        <v>45366</v>
+      </c>
+      <c r="F27" s="2">
+        <v>46371</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" s="1">
+        <v>100</v>
+      </c>
+      <c r="K27" s="1">
+        <v>100</v>
+      </c>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
         <v>53</v>
       </c>
@@ -5418,8 +6305,33 @@
       <c r="D28" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E28" s="2">
+        <v>45366</v>
+      </c>
+      <c r="F28" s="2">
+        <v>46736</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="1">
+        <v>100</v>
+      </c>
+      <c r="K28" s="1">
+        <v>100</v>
+      </c>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>54</v>
       </c>
@@ -5432,8 +6344,33 @@
       <c r="D29" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E29" s="2">
+        <v>45412</v>
+      </c>
+      <c r="F29" s="2">
+        <v>46112</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J29" s="1">
+        <v>100</v>
+      </c>
+      <c r="K29" s="1">
+        <v>100</v>
+      </c>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
         <v>55</v>
       </c>
@@ -5446,8 +6383,33 @@
       <c r="D30" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E30" s="2">
+        <v>45429</v>
+      </c>
+      <c r="F30" s="2">
+        <v>46477</v>
+      </c>
+      <c r="G30" s="3">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" s="1">
+        <v>100</v>
+      </c>
+      <c r="K30" s="1">
+        <v>100</v>
+      </c>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>56</v>
       </c>
@@ -5460,16 +6422,66 @@
       <c r="D31" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E31" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F31" s="2">
+        <v>46325</v>
+      </c>
+      <c r="G31" s="3">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="1">
+        <v>100</v>
+      </c>
+      <c r="K31" s="1">
+        <v>100</v>
+      </c>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
         <v>57</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E32" s="2">
+        <v>45350</v>
+      </c>
+      <c r="F32" s="2">
+        <v>46203</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" s="1">
+        <v>100</v>
+      </c>
+      <c r="K32" s="1">
+        <v>100</v>
+      </c>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>59</v>
       </c>
@@ -5482,8 +6494,31 @@
       <c r="D33" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E33" s="2"/>
+      <c r="F33" s="2">
+        <v>46142</v>
+      </c>
+      <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="1">
+        <v>100</v>
+      </c>
+      <c r="K33" s="1">
+        <v>100</v>
+      </c>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
         <v>123</v>
       </c>
@@ -5496,8 +6531,31 @@
       <c r="D34" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E34" s="1"/>
+      <c r="F34" s="2">
+        <v>46080</v>
+      </c>
+      <c r="G34" s="3">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="1">
+        <v>100</v>
+      </c>
+      <c r="K34" s="1">
+        <v>100</v>
+      </c>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>125</v>
       </c>
@@ -5510,8 +6568,31 @@
       <c r="D35" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E35" s="1"/>
+      <c r="F35" s="2">
+        <v>46129</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="1">
+        <v>100</v>
+      </c>
+      <c r="K35" s="1">
+        <v>100</v>
+      </c>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
         <v>126</v>
       </c>
@@ -5524,8 +6605,31 @@
       <c r="D36" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E36" s="1"/>
+      <c r="F36" s="2">
+        <v>46097</v>
+      </c>
+      <c r="G36" s="3">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="1">
+        <v>100</v>
+      </c>
+      <c r="K36" s="1">
+        <v>100</v>
+      </c>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>127</v>
       </c>
@@ -5538,8 +6642,31 @@
       <c r="D37" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E37" s="1"/>
+      <c r="F37" s="2">
+        <v>46142</v>
+      </c>
+      <c r="G37" s="3">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="1">
+        <v>100</v>
+      </c>
+      <c r="K37" s="1">
+        <v>100</v>
+      </c>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
         <v>128</v>
       </c>
@@ -5552,8 +6679,31 @@
       <c r="D38" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E38" s="1"/>
+      <c r="F38" s="2">
+        <v>46171</v>
+      </c>
+      <c r="G38" s="3">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" s="1">
+        <v>100</v>
+      </c>
+      <c r="K38" s="1">
+        <v>100</v>
+      </c>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>129</v>
       </c>
@@ -5566,8 +6716,31 @@
       <c r="D39" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E39" s="1"/>
+      <c r="F39" s="2">
+        <v>46234</v>
+      </c>
+      <c r="G39" s="3">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J39" s="1">
+        <v>100</v>
+      </c>
+      <c r="K39" s="1">
+        <v>100</v>
+      </c>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
         <v>130</v>
       </c>
@@ -5580,8 +6753,31 @@
       <c r="D40" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E40" s="1"/>
+      <c r="F40" s="2">
+        <v>46265</v>
+      </c>
+      <c r="G40" s="3">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="1">
+        <v>100</v>
+      </c>
+      <c r="K40" s="1">
+        <v>100</v>
+      </c>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
         <v>131</v>
       </c>
@@ -5594,8 +6790,31 @@
       <c r="D41" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E41" s="1"/>
+      <c r="F41" s="2">
+        <v>46325</v>
+      </c>
+      <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" s="1">
+        <v>100</v>
+      </c>
+      <c r="K41" s="1">
+        <v>100</v>
+      </c>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
         <v>132</v>
       </c>
@@ -5608,8 +6827,31 @@
       <c r="D42" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E42" s="1"/>
+      <c r="F42" s="2">
+        <v>46356</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" s="1">
+        <v>100</v>
+      </c>
+      <c r="K42" s="1">
+        <v>100</v>
+      </c>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="s">
         <v>134</v>
       </c>
@@ -5622,8 +6864,31 @@
       <c r="D43" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E43" s="1"/>
+      <c r="F43" s="2">
+        <v>46203</v>
+      </c>
+      <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" s="1">
+        <v>100</v>
+      </c>
+      <c r="K43" s="1">
+        <v>100</v>
+      </c>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="s">
         <v>135</v>
       </c>
@@ -5636,8 +6901,31 @@
       <c r="D44" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E44" s="1"/>
+      <c r="F44" s="2">
+        <v>46402</v>
+      </c>
+      <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" s="1">
+        <v>100</v>
+      </c>
+      <c r="K44" s="1">
+        <v>100</v>
+      </c>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>136</v>
       </c>
@@ -5650,8 +6938,31 @@
       <c r="D45" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E45" s="1"/>
+      <c r="F45" s="2">
+        <v>46507</v>
+      </c>
+      <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J45" s="1">
+        <v>100</v>
+      </c>
+      <c r="K45" s="1">
+        <v>100</v>
+      </c>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
         <v>137</v>
       </c>
@@ -5664,8 +6975,31 @@
       <c r="D46" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E46" s="1"/>
+      <c r="F46" s="2">
+        <v>46538</v>
+      </c>
+      <c r="G46" s="3">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" s="1">
+        <v>100</v>
+      </c>
+      <c r="K46" s="1">
+        <v>100</v>
+      </c>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>138</v>
       </c>
@@ -5678,8 +7012,31 @@
       <c r="D47" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E47" s="1"/>
+      <c r="F47" s="2">
+        <v>46568</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J47" s="1">
+        <v>100</v>
+      </c>
+      <c r="K47" s="1">
+        <v>100</v>
+      </c>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="10" t="s">
         <v>60</v>
       </c>
@@ -5692,8 +7049,33 @@
       <c r="D48" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E48" s="2">
+        <v>45296</v>
+      </c>
+      <c r="F48" s="2">
+        <v>46691</v>
+      </c>
+      <c r="G48" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="H48" s="1">
+        <v>2</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J48" s="1">
+        <v>100</v>
+      </c>
+      <c r="K48" s="1">
+        <v>100</v>
+      </c>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>61</v>
       </c>
@@ -5706,8 +7088,33 @@
       <c r="D49" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E49" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F49" s="2">
+        <v>46691</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="H49" s="1">
+        <v>2</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J49" s="1">
+        <v>100</v>
+      </c>
+      <c r="K49" s="1">
+        <v>100</v>
+      </c>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="s">
         <v>62</v>
       </c>
@@ -5720,8 +7127,31 @@
       <c r="D50" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E50" s="2"/>
+      <c r="F50" s="2">
+        <v>46691</v>
+      </c>
+      <c r="G50" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="H50" s="1">
+        <v>2</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J50" s="1">
+        <v>100</v>
+      </c>
+      <c r="K50" s="1">
+        <v>100</v>
+      </c>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>63</v>
       </c>
@@ -5734,8 +7164,33 @@
       <c r="D51" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E51" s="2">
+        <v>45352</v>
+      </c>
+      <c r="F51" s="2">
+        <v>46691</v>
+      </c>
+      <c r="G51" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="H51" s="1">
+        <v>2</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J51" s="1">
+        <v>100</v>
+      </c>
+      <c r="K51" s="1">
+        <v>100</v>
+      </c>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
         <v>74</v>
       </c>
@@ -5748,8 +7203,31 @@
       <c r="D52" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E52" s="2"/>
+      <c r="F52" s="2">
+        <v>46173</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="H52" s="1">
+        <v>4</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J52" s="1">
+        <v>100</v>
+      </c>
+      <c r="K52" s="1">
+        <v>67</v>
+      </c>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>77</v>
       </c>
@@ -5762,8 +7240,31 @@
       <c r="D53" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E53" s="2"/>
+      <c r="F53" s="2">
+        <v>46805</v>
+      </c>
+      <c r="G53" s="3">
+        <v>0.35920000000000002</v>
+      </c>
+      <c r="H53" s="1">
+        <v>4</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J53" s="1">
+        <v>100</v>
+      </c>
+      <c r="K53" s="1">
+        <v>100</v>
+      </c>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="10" t="s">
         <v>78</v>
       </c>
@@ -5776,8 +7277,31 @@
       <c r="D54" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E54" s="2"/>
+      <c r="F54" s="2">
+        <v>48397</v>
+      </c>
+      <c r="G54" s="3">
+        <v>6.6299999999999998E-2</v>
+      </c>
+      <c r="H54" s="1">
+        <v>2</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J54" s="1">
+        <v>100</v>
+      </c>
+      <c r="K54" s="1">
+        <v>100</v>
+      </c>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>79</v>
       </c>
@@ -5790,8 +7314,31 @@
       <c r="D55" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E55" s="2"/>
+      <c r="F55" s="2">
+        <v>50284</v>
+      </c>
+      <c r="G55" s="3">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="H55" s="1">
+        <v>2</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J55" s="1">
+        <v>100</v>
+      </c>
+      <c r="K55" s="1">
+        <v>100</v>
+      </c>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="10" t="s">
         <v>80</v>
       </c>
@@ -5804,8 +7351,31 @@
       <c r="D56" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E56" s="2"/>
+      <c r="F56" s="2">
+        <v>50284</v>
+      </c>
+      <c r="G56" s="3">
+        <v>6.6299999999999998E-2</v>
+      </c>
+      <c r="H56" s="1">
+        <v>2</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J56" s="1">
+        <v>100</v>
+      </c>
+      <c r="K56" s="1">
+        <v>91.84</v>
+      </c>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="s">
         <v>83</v>
       </c>
@@ -5818,8 +7388,31 @@
       <c r="D57" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E57" s="2"/>
+      <c r="F57" s="2">
+        <v>46084</v>
+      </c>
+      <c r="G57" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="H57" s="1">
+        <v>2</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J57" s="1">
+        <v>100</v>
+      </c>
+      <c r="K57" s="1">
+        <v>100</v>
+      </c>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="10" t="s">
         <v>84</v>
       </c>
@@ -5832,8 +7425,31 @@
       <c r="D58" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <v>46092</v>
+      </c>
+      <c r="G58" s="3">
+        <v>7.4899999999999994E-2</v>
+      </c>
+      <c r="H58" s="1">
+        <v>2</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J58" s="1">
+        <v>100</v>
+      </c>
+      <c r="K58" s="1">
+        <v>100</v>
+      </c>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="10" t="s">
         <v>85</v>
       </c>
@@ -5846,8 +7462,31 @@
       <c r="D59" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E59" s="2"/>
+      <c r="F59" s="2">
+        <v>46170</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0.06</v>
+      </c>
+      <c r="H59" s="1">
+        <v>4</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J59" s="1">
+        <v>100</v>
+      </c>
+      <c r="K59" s="1">
+        <v>100</v>
+      </c>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="10" t="s">
         <v>86</v>
       </c>
@@ -5860,8 +7499,31 @@
       <c r="D60" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E60" s="1"/>
+      <c r="F60" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G60" s="3">
+        <v>0.06</v>
+      </c>
+      <c r="H60" s="1">
+        <v>4</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J60" s="1">
+        <v>100</v>
+      </c>
+      <c r="K60" s="1">
+        <v>100</v>
+      </c>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="10" t="s">
         <v>87</v>
       </c>
@@ -5874,8 +7536,31 @@
       <c r="D61" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E61" s="1"/>
+      <c r="F61" s="2">
+        <v>46348</v>
+      </c>
+      <c r="G61" s="3">
+        <v>9.7500000000000003E-2</v>
+      </c>
+      <c r="H61" s="1">
+        <v>2</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J61" s="1">
+        <v>100</v>
+      </c>
+      <c r="K61" s="1">
+        <v>100</v>
+      </c>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="10" t="s">
         <v>88</v>
       </c>
@@ -5888,8 +7573,31 @@
       <c r="D62" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E62" s="1"/>
+      <c r="F62" s="2">
+        <v>46683</v>
+      </c>
+      <c r="G62" s="3">
+        <v>5.7500000000000002E-2</v>
+      </c>
+      <c r="H62" s="1">
+        <v>2</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J62" s="1">
+        <v>100</v>
+      </c>
+      <c r="K62" s="1">
+        <v>100</v>
+      </c>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="10" t="s">
         <v>89</v>
       </c>
@@ -5902,8 +7610,31 @@
       <c r="D63" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E63" s="1"/>
+      <c r="F63" s="2">
+        <v>47070</v>
+      </c>
+      <c r="G63" s="3">
+        <v>6.25E-2</v>
+      </c>
+      <c r="H63" s="1">
+        <v>2</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J63" s="1">
+        <v>100</v>
+      </c>
+      <c r="K63" s="1">
+        <v>100</v>
+      </c>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="10" t="s">
         <v>90</v>
       </c>
@@ -5916,8 +7647,31 @@
       <c r="D64" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E64" s="1"/>
+      <c r="F64" s="2">
+        <v>47388</v>
+      </c>
+      <c r="G64" s="3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H64" s="1">
+        <v>2</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J64" s="1">
+        <v>100</v>
+      </c>
+      <c r="K64" s="1">
+        <v>100</v>
+      </c>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
         <v>91</v>
       </c>
@@ -5930,8 +7684,31 @@
       <c r="D65" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E65" s="1"/>
+      <c r="F65" s="2">
+        <v>47414</v>
+      </c>
+      <c r="G65" s="3">
+        <v>7.2499999999999995E-2</v>
+      </c>
+      <c r="H65" s="1">
+        <v>2</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J65" s="1">
+        <v>100</v>
+      </c>
+      <c r="K65" s="1">
+        <v>100</v>
+      </c>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="10" t="s">
         <v>92</v>
       </c>
@@ -5944,8 +7721,31 @@
       <c r="D66" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E66" s="2"/>
+      <c r="F66" s="2">
+        <v>47357</v>
+      </c>
+      <c r="G66" s="3">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="H66" s="1">
+        <v>2</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J66" s="1">
+        <v>100</v>
+      </c>
+      <c r="K66" s="1">
+        <v>100</v>
+      </c>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="10" t="s">
         <v>93</v>
       </c>
@@ -5958,8 +7758,31 @@
       <c r="D67" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E67" s="2"/>
+      <c r="F67" s="2">
+        <v>48131</v>
+      </c>
+      <c r="G67" s="3">
+        <v>7.6499999999999999E-2</v>
+      </c>
+      <c r="H67" s="1">
+        <v>2</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J67" s="1">
+        <v>100</v>
+      </c>
+      <c r="K67" s="1">
+        <v>100</v>
+      </c>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="10" t="s">
         <v>94</v>
       </c>
@@ -5972,8 +7795,31 @@
       <c r="D68" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E68" s="1"/>
+      <c r="F68" s="2">
+        <v>48165</v>
+      </c>
+      <c r="G68" s="3">
+        <v>7.2499999999999995E-2</v>
+      </c>
+      <c r="H68" s="1">
+        <v>2</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J68" s="1">
+        <v>100</v>
+      </c>
+      <c r="K68" s="1">
+        <v>100</v>
+      </c>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="10" t="s">
         <v>95</v>
       </c>
@@ -5986,8 +7832,31 @@
       <c r="D69" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E69" s="1"/>
+      <c r="F69" s="2">
+        <v>48727</v>
+      </c>
+      <c r="G69" s="3">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="H69" s="1">
+        <v>2</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J69" s="1">
+        <v>100</v>
+      </c>
+      <c r="K69" s="1">
+        <v>100</v>
+      </c>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="10" t="s">
         <v>96</v>
       </c>
@@ -6000,8 +7869,31 @@
       <c r="D70" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E70" s="1"/>
+      <c r="F70" s="2">
+        <v>46203</v>
+      </c>
+      <c r="G70" s="3">
+        <v>0.1095</v>
+      </c>
+      <c r="H70" s="1">
+        <v>4</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J70" s="1">
+        <v>100</v>
+      </c>
+      <c r="K70" s="1">
+        <v>100</v>
+      </c>
+      <c r="L70" s="1"/>
+      <c r="M70" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="10" t="s">
         <v>97</v>
       </c>
@@ -6014,8 +7906,31 @@
       <c r="D71" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E71" s="1"/>
+      <c r="F71" s="2">
+        <v>46221</v>
+      </c>
+      <c r="G71" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="H71" s="1">
+        <v>2</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J71" s="1">
+        <v>100</v>
+      </c>
+      <c r="K71" s="1">
+        <v>100</v>
+      </c>
+      <c r="L71" s="1"/>
+      <c r="M71" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="10" t="s">
         <v>98</v>
       </c>
@@ -6028,8 +7943,31 @@
       <c r="D72" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E72" s="1"/>
+      <c r="F72" s="2">
+        <v>46507</v>
+      </c>
+      <c r="G72" s="3">
+        <v>9.1300000000000006E-2</v>
+      </c>
+      <c r="H72" s="1">
+        <v>2</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J72" s="1">
+        <v>100</v>
+      </c>
+      <c r="K72" s="1">
+        <v>100</v>
+      </c>
+      <c r="L72" s="1"/>
+      <c r="M72" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="10" t="s">
         <v>99</v>
       </c>
@@ -6042,8 +7980,31 @@
       <c r="D73" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E73" s="1"/>
+      <c r="F73" s="2">
+        <v>47292</v>
+      </c>
+      <c r="G73" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="H73" s="1">
+        <v>2</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J73" s="1">
+        <v>100</v>
+      </c>
+      <c r="K73" s="1">
+        <v>100</v>
+      </c>
+      <c r="L73" s="1"/>
+      <c r="M73" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="10" t="s">
         <v>100</v>
       </c>
@@ -6056,8 +8017,31 @@
       <c r="D74" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E74" s="1"/>
+      <c r="F74" s="2">
+        <v>47299</v>
+      </c>
+      <c r="G74" s="3">
+        <v>0.09</v>
+      </c>
+      <c r="H74" s="1">
+        <v>2</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J74" s="1">
+        <v>100</v>
+      </c>
+      <c r="K74" s="1">
+        <v>100</v>
+      </c>
+      <c r="L74" s="1"/>
+      <c r="M74" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="10" t="s">
         <v>101</v>
       </c>
@@ -6070,8 +8054,31 @@
       <c r="D75" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E75" s="1"/>
+      <c r="F75" s="2">
+        <v>47686</v>
+      </c>
+      <c r="G75" s="3">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="H75" s="1">
+        <v>2</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J75" s="1">
+        <v>100</v>
+      </c>
+      <c r="K75" s="1">
+        <v>100</v>
+      </c>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="10" t="s">
         <v>102</v>
       </c>
@@ -6084,8 +8091,31 @@
       <c r="D76" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E76" s="2"/>
+      <c r="F76" s="2">
+        <v>48047</v>
+      </c>
+      <c r="G76" s="3">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="H76" s="1">
+        <v>2</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J76" s="1">
+        <v>100</v>
+      </c>
+      <c r="K76" s="1">
+        <v>100</v>
+      </c>
+      <c r="L76" s="1"/>
+      <c r="M76" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="10" t="s">
         <v>103</v>
       </c>
@@ -6098,8 +8128,31 @@
       <c r="D77" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E77" s="1"/>
+      <c r="F77" s="2">
+        <v>48102</v>
+      </c>
+      <c r="G77" s="3">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="H77" s="1">
+        <v>2</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J77" s="1">
+        <v>100</v>
+      </c>
+      <c r="K77" s="1">
+        <v>100</v>
+      </c>
+      <c r="L77" s="1"/>
+      <c r="M77" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="10" t="s">
         <v>104</v>
       </c>
@@ -6112,8 +8165,31 @@
       <c r="D78" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E78" s="2"/>
+      <c r="F78" s="2">
+        <v>48364</v>
+      </c>
+      <c r="G78" s="3">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="H78" s="1">
+        <v>2</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J78" s="1">
+        <v>100</v>
+      </c>
+      <c r="K78" s="1">
+        <v>100</v>
+      </c>
+      <c r="L78" s="1"/>
+      <c r="M78" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="10" t="s">
         <v>105</v>
       </c>
@@ -6126,8 +8202,31 @@
       <c r="D79" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E79" s="2"/>
+      <c r="F79" s="2">
+        <v>48503</v>
+      </c>
+      <c r="G79" s="3">
+        <v>7.8799999999999995E-2</v>
+      </c>
+      <c r="H79" s="1">
+        <v>2</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J79" s="1">
+        <v>100</v>
+      </c>
+      <c r="K79" s="1">
+        <v>100</v>
+      </c>
+      <c r="L79" s="1"/>
+      <c r="M79" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="10" t="s">
         <v>106</v>
       </c>
@@ -6140,8 +8239,31 @@
       <c r="D80" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E80" s="2"/>
+      <c r="F80" s="2">
+        <v>48740</v>
+      </c>
+      <c r="G80" s="3">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="H80" s="1">
+        <v>2</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J80" s="1">
+        <v>100</v>
+      </c>
+      <c r="K80" s="1">
+        <v>100</v>
+      </c>
+      <c r="L80" s="1"/>
+      <c r="M80" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="10" t="s">
         <v>107</v>
       </c>
@@ -6154,8 +8276,31 @@
       <c r="D81" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E81" s="2"/>
+      <c r="F81" s="2">
+        <v>48852</v>
+      </c>
+      <c r="G81" s="3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H81" s="1">
+        <v>2</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J81" s="1">
+        <v>100</v>
+      </c>
+      <c r="K81" s="1">
+        <v>100</v>
+      </c>
+      <c r="L81" s="1"/>
+      <c r="M81" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="10" t="s">
         <v>108</v>
       </c>
@@ -6168,8 +8313,31 @@
       <c r="D82" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E82" s="1"/>
+      <c r="F82" s="2">
+        <v>49399</v>
+      </c>
+      <c r="G82" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="H82" s="1">
+        <v>2</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J82" s="1">
+        <v>100</v>
+      </c>
+      <c r="K82" s="1">
+        <v>100</v>
+      </c>
+      <c r="L82" s="1"/>
+      <c r="M82" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="10" t="s">
         <v>109</v>
       </c>
@@ -6182,8 +8350,31 @@
       <c r="D83" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E83" s="1"/>
+      <c r="F83" s="2">
+        <v>49653</v>
+      </c>
+      <c r="G83" s="3">
+        <v>7.6300000000000007E-2</v>
+      </c>
+      <c r="H83" s="1">
+        <v>2</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J83" s="1">
+        <v>100</v>
+      </c>
+      <c r="K83" s="1">
+        <v>100</v>
+      </c>
+      <c r="L83" s="1"/>
+      <c r="M83" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="10" t="s">
         <v>110</v>
       </c>
@@ -6196,8 +8387,126 @@
       <c r="D84" s="10" t="s">
         <v>18</v>
       </c>
+      <c r="E84" s="1"/>
+      <c r="F84" s="2">
+        <v>48961</v>
+      </c>
+      <c r="G84" s="3">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="H84" s="1">
+        <v>2</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J84" s="1">
+        <v>100</v>
+      </c>
+      <c r="K84" s="1">
+        <v>100</v>
+      </c>
+      <c r="L84" s="1"/>
+      <c r="M84" s="1" t="s">
+        <v>121</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="F1:F6">
+    <cfRule type="cellIs" dxfId="18" priority="19" operator="lessThan">
+      <formula>TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7">
+    <cfRule type="cellIs" dxfId="17" priority="18" operator="lessThan">
+      <formula>TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="lessThan">
+      <formula>TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9">
+    <cfRule type="cellIs" dxfId="15" priority="16" operator="lessThan">
+      <formula>TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10">
+    <cfRule type="cellIs" dxfId="14" priority="15" operator="lessThan">
+      <formula>TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11">
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="lessThan">
+      <formula>TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="cellIs" dxfId="12" priority="13" operator="lessThan">
+      <formula>TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13">
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="lessThan">
+      <formula>TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="lessThan">
+      <formula>TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="lessThan">
+      <formula>TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="lessThan">
+      <formula>TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="lessThan">
+      <formula>TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18:F19">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="lessThan">
+      <formula>TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20:F22">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThan">
+      <formula>TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23:F33">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
+      <formula>TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F34:F51">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
+      <formula>TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F52">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+      <formula>TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F53:F56">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+      <formula>TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F57:F84">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
